--- a/companies/alder-ridge/source-files/Shared/Finance/Treasury/FY27 working/treasury outlook support - July v8 controller tie.xlsx
+++ b/companies/alder-ridge/source-files/Shared/Finance/Treasury/FY27 working/treasury outlook support - July v8 controller tie.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" r:id="R73e211e6a096475d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash and Liquidity" sheetId="2" r:id="Raf6fb7c911f3425e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt and Hedges" sheetId="3" r:id="R1eba90348f0e46e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bank Economics" sheetId="4" r:id="R88d54a88797a4838"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Credit Outlook" sheetId="5" r:id="R93c77e60782945c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Checks" sheetId="6" r:id="Re907c515da09426f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" r:id="R8272e23d845a4270"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash and Liquidity" sheetId="2" r:id="R75945bd9ea214746"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt and Hedges" sheetId="3" r:id="R8afc2131a1a94918"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bank Economics" sheetId="4" r:id="Refa384e2751b4500"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Credit Outlook" sheetId="5" r:id="Rf1c4b36a38ba4b5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Checks" sheetId="6" r:id="Rc0e8f60703dc449f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -265,7 +265,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:personList xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:person displayName="Alder Ridge Finance" id="{39E7F9E7-94EF-43E5-99C6-06F4BB69A95A}"/>
+  <xltc:person displayName="Alder Ridge Finance" id="{005012E2-F4E6-4913-91FB-9369B582B27F}"/>
 </xltc:personList>
 </file>
 
@@ -2375,7 +2375,7 @@
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="37" t="str">
-        <x:v>TRY-00475</x:v>
+        <x:v>TRY-00493</x:v>
       </x:c>
       <x:c r="B52" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -2414,7 +2414,7 @@
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="37" t="str">
-        <x:v>TRY-00476</x:v>
+        <x:v>TRY-00494</x:v>
       </x:c>
       <x:c r="B53" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -2451,7 +2451,7 @@
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="37" t="str">
-        <x:v>TRY-00477</x:v>
+        <x:v>TRY-00495</x:v>
       </x:c>
       <x:c r="B54" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -2488,7 +2488,7 @@
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="37" t="str">
-        <x:v>TRY-00478</x:v>
+        <x:v>TRY-00496</x:v>
       </x:c>
       <x:c r="B55" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -2525,7 +2525,7 @@
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="37" t="str">
-        <x:v>TRY-00479</x:v>
+        <x:v>TRY-00497</x:v>
       </x:c>
       <x:c r="B56" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -2562,7 +2562,7 @@
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="37" t="str">
-        <x:v>TRY-00480</x:v>
+        <x:v>TRY-00498</x:v>
       </x:c>
       <x:c r="B57" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -2599,7 +2599,7 @@
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="37" t="str">
-        <x:v>TRY-00481</x:v>
+        <x:v>TRY-00499</x:v>
       </x:c>
       <x:c r="B58" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -2636,7 +2636,7 @@
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="37" t="str">
-        <x:v>TRY-00482</x:v>
+        <x:v>TRY-00500</x:v>
       </x:c>
       <x:c r="B59" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -2673,7 +2673,7 @@
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="37" t="str">
-        <x:v>TRY-00483</x:v>
+        <x:v>TRY-00501</x:v>
       </x:c>
       <x:c r="B60" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -2710,7 +2710,7 @@
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="37" t="str">
-        <x:v>TRY-00484</x:v>
+        <x:v>TRY-00502</x:v>
       </x:c>
       <x:c r="B61" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -2747,7 +2747,7 @@
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="37" t="str">
-        <x:v>TRY-00485</x:v>
+        <x:v>TRY-00503</x:v>
       </x:c>
       <x:c r="B62" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -2784,7 +2784,7 @@
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="37" t="str">
-        <x:v>TRY-00486</x:v>
+        <x:v>TRY-00504</x:v>
       </x:c>
       <x:c r="B63" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -2821,7 +2821,7 @@
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="37" t="str">
-        <x:v>TRY-00487</x:v>
+        <x:v>TRY-00505</x:v>
       </x:c>
       <x:c r="B64" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -2858,7 +2858,7 @@
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="37" t="str">
-        <x:v>TRY-00488</x:v>
+        <x:v>TRY-00506</x:v>
       </x:c>
       <x:c r="B65" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -2895,7 +2895,7 @@
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="37" t="str">
-        <x:v>TRY-00489</x:v>
+        <x:v>TRY-00507</x:v>
       </x:c>
       <x:c r="B66" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -2932,7 +2932,7 @@
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="37" t="str">
-        <x:v>TRY-00490</x:v>
+        <x:v>TRY-00508</x:v>
       </x:c>
       <x:c r="B67" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -2969,7 +2969,7 @@
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="37" t="str">
-        <x:v>TRY-00491</x:v>
+        <x:v>TRY-00509</x:v>
       </x:c>
       <x:c r="B68" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -3006,7 +3006,7 @@
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="37" t="str">
-        <x:v>TRY-00492</x:v>
+        <x:v>TRY-00510</x:v>
       </x:c>
       <x:c r="B69" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -3043,7 +3043,7 @@
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="37" t="str">
-        <x:v>TRY-00493</x:v>
+        <x:v>TRY-00511</x:v>
       </x:c>
       <x:c r="B70" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -3080,7 +3080,7 @@
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="37" t="str">
-        <x:v>TRY-00494</x:v>
+        <x:v>TRY-00512</x:v>
       </x:c>
       <x:c r="B71" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -3117,7 +3117,7 @@
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="37" t="str">
-        <x:v>TRY-00495</x:v>
+        <x:v>TRY-00513</x:v>
       </x:c>
       <x:c r="B72" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -3154,7 +3154,7 @@
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="37" t="str">
-        <x:v>TRY-00496</x:v>
+        <x:v>TRY-00514</x:v>
       </x:c>
       <x:c r="B73" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -3191,7 +3191,7 @@
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="37" t="str">
-        <x:v>TRY-00497</x:v>
+        <x:v>TRY-00515</x:v>
       </x:c>
       <x:c r="B74" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -3228,7 +3228,7 @@
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="37" t="str">
-        <x:v>TRY-00498</x:v>
+        <x:v>TRY-00516</x:v>
       </x:c>
       <x:c r="B75" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -3265,7 +3265,7 @@
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="37" t="str">
-        <x:v>TRY-00499</x:v>
+        <x:v>TRY-00517</x:v>
       </x:c>
       <x:c r="B76" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -3302,7 +3302,7 @@
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="37" t="str">
-        <x:v>TRY-00500</x:v>
+        <x:v>TRY-00518</x:v>
       </x:c>
       <x:c r="B77" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -3339,7 +3339,7 @@
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="37" t="str">
-        <x:v>TRY-00501</x:v>
+        <x:v>TRY-00519</x:v>
       </x:c>
       <x:c r="B78" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -3376,7 +3376,7 @@
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="37" t="str">
-        <x:v>TRY-00502</x:v>
+        <x:v>TRY-00520</x:v>
       </x:c>
       <x:c r="B79" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -3413,7 +3413,7 @@
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="37" t="str">
-        <x:v>TRY-00503</x:v>
+        <x:v>TRY-00521</x:v>
       </x:c>
       <x:c r="B80" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -3450,7 +3450,7 @@
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="37" t="str">
-        <x:v>TRY-00504</x:v>
+        <x:v>TRY-00522</x:v>
       </x:c>
       <x:c r="B81" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -3487,7 +3487,7 @@
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="37" t="str">
-        <x:v>TRY-00505</x:v>
+        <x:v>TRY-00523</x:v>
       </x:c>
       <x:c r="B82" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -3524,7 +3524,7 @@
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="37" t="str">
-        <x:v>TRY-00506</x:v>
+        <x:v>TRY-00524</x:v>
       </x:c>
       <x:c r="B83" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -3561,7 +3561,7 @@
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="37" t="str">
-        <x:v>TRY-00507</x:v>
+        <x:v>TRY-00525</x:v>
       </x:c>
       <x:c r="B84" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -3598,7 +3598,7 @@
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="37" t="str">
-        <x:v>TRY-00508</x:v>
+        <x:v>TRY-00526</x:v>
       </x:c>
       <x:c r="B85" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -3635,7 +3635,7 @@
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="37" t="str">
-        <x:v>TRY-00509</x:v>
+        <x:v>TRY-00527</x:v>
       </x:c>
       <x:c r="B86" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -3672,7 +3672,7 @@
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="37" t="str">
-        <x:v>TRY-00510</x:v>
+        <x:v>TRY-00528</x:v>
       </x:c>
       <x:c r="B87" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -3709,7 +3709,7 @@
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="37" t="str">
-        <x:v>TRY-00511</x:v>
+        <x:v>TRY-00529</x:v>
       </x:c>
       <x:c r="B88" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -3746,7 +3746,7 @@
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="37" t="str">
-        <x:v>TRY-00512</x:v>
+        <x:v>TRY-00530</x:v>
       </x:c>
       <x:c r="B89" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -3783,7 +3783,7 @@
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="37" t="str">
-        <x:v>TRY-00513</x:v>
+        <x:v>TRY-00531</x:v>
       </x:c>
       <x:c r="B90" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -3820,7 +3820,7 @@
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="37" t="str">
-        <x:v>TRY-00514</x:v>
+        <x:v>TRY-00532</x:v>
       </x:c>
       <x:c r="B91" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -3857,7 +3857,7 @@
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="37" t="str">
-        <x:v>TRY-00515</x:v>
+        <x:v>TRY-00533</x:v>
       </x:c>
       <x:c r="B92" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -3894,7 +3894,7 @@
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="37" t="str">
-        <x:v>TRY-00516</x:v>
+        <x:v>TRY-00534</x:v>
       </x:c>
       <x:c r="B93" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -3931,7 +3931,7 @@
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="37" t="str">
-        <x:v>TRY-00517</x:v>
+        <x:v>TRY-00535</x:v>
       </x:c>
       <x:c r="B94" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -3968,7 +3968,7 @@
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="37" t="str">
-        <x:v>TRY-00518</x:v>
+        <x:v>TRY-00536</x:v>
       </x:c>
       <x:c r="B95" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -4005,7 +4005,7 @@
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="37" t="str">
-        <x:v>TRY-00519</x:v>
+        <x:v>TRY-00537</x:v>
       </x:c>
       <x:c r="B96" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -4042,7 +4042,7 @@
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="37" t="str">
-        <x:v>TRY-00520</x:v>
+        <x:v>TRY-00538</x:v>
       </x:c>
       <x:c r="B97" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -4079,7 +4079,7 @@
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="37" t="str">
-        <x:v>TRY-00521</x:v>
+        <x:v>TRY-00539</x:v>
       </x:c>
       <x:c r="B98" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -4116,7 +4116,7 @@
     </x:row>
     <x:row r="99">
       <x:c r="A99" s="37" t="str">
-        <x:v>TRY-00522</x:v>
+        <x:v>TRY-00540</x:v>
       </x:c>
       <x:c r="B99" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -4153,7 +4153,7 @@
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="37" t="str">
-        <x:v>TRY-00523</x:v>
+        <x:v>TRY-00541</x:v>
       </x:c>
       <x:c r="B100" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -4190,7 +4190,7 @@
     </x:row>
     <x:row r="101">
       <x:c r="A101" s="37" t="str">
-        <x:v>TRY-00524</x:v>
+        <x:v>TRY-00542</x:v>
       </x:c>
       <x:c r="B101" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -4227,7 +4227,7 @@
     </x:row>
     <x:row r="102">
       <x:c r="A102" s="37" t="str">
-        <x:v>TRY-00525</x:v>
+        <x:v>TRY-00543</x:v>
       </x:c>
       <x:c r="B102" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -4264,7 +4264,7 @@
     </x:row>
     <x:row r="103">
       <x:c r="A103" s="37" t="str">
-        <x:v>TRY-00526</x:v>
+        <x:v>TRY-00544</x:v>
       </x:c>
       <x:c r="B103" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -4301,7 +4301,7 @@
     </x:row>
     <x:row r="104">
       <x:c r="A104" s="37" t="str">
-        <x:v>TRY-00527</x:v>
+        <x:v>TRY-00545</x:v>
       </x:c>
       <x:c r="B104" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -4338,7 +4338,7 @@
     </x:row>
     <x:row r="105">
       <x:c r="A105" s="37" t="str">
-        <x:v>TRY-00528</x:v>
+        <x:v>TRY-00546</x:v>
       </x:c>
       <x:c r="B105" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -4375,7 +4375,7 @@
     </x:row>
     <x:row r="106">
       <x:c r="A106" s="37" t="str">
-        <x:v>TRY-00529</x:v>
+        <x:v>TRY-00547</x:v>
       </x:c>
       <x:c r="B106" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -4412,7 +4412,7 @@
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="37" t="str">
-        <x:v>TRY-00530</x:v>
+        <x:v>TRY-00548</x:v>
       </x:c>
       <x:c r="B107" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -4449,7 +4449,7 @@
     </x:row>
     <x:row r="108">
       <x:c r="A108" s="37" t="str">
-        <x:v>TRY-00531</x:v>
+        <x:v>TRY-00549</x:v>
       </x:c>
       <x:c r="B108" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -4486,7 +4486,7 @@
     </x:row>
     <x:row r="109">
       <x:c r="A109" s="37" t="str">
-        <x:v>TRY-00532</x:v>
+        <x:v>TRY-00550</x:v>
       </x:c>
       <x:c r="B109" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -4523,7 +4523,7 @@
     </x:row>
     <x:row r="110">
       <x:c r="A110" s="37" t="str">
-        <x:v>TRY-00533</x:v>
+        <x:v>TRY-00551</x:v>
       </x:c>
       <x:c r="B110" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -4560,7 +4560,7 @@
     </x:row>
     <x:row r="111">
       <x:c r="A111" s="37" t="str">
-        <x:v>TRY-00550</x:v>
+        <x:v>TRY-00568</x:v>
       </x:c>
       <x:c r="B111" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -4597,7 +4597,7 @@
     </x:row>
     <x:row r="112">
       <x:c r="A112" s="37" t="str">
-        <x:v>TRY-00551</x:v>
+        <x:v>TRY-00569</x:v>
       </x:c>
       <x:c r="B112" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -4634,7 +4634,7 @@
     </x:row>
     <x:row r="113">
       <x:c r="A113" s="37" t="str">
-        <x:v>TRY-00552</x:v>
+        <x:v>TRY-00570</x:v>
       </x:c>
       <x:c r="B113" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -4671,7 +4671,7 @@
     </x:row>
     <x:row r="114">
       <x:c r="A114" s="37" t="str">
-        <x:v>TRY-00553</x:v>
+        <x:v>TRY-00571</x:v>
       </x:c>
       <x:c r="B114" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -4708,7 +4708,7 @@
     </x:row>
     <x:row r="115">
       <x:c r="A115" s="37" t="str">
-        <x:v>TRY-00554</x:v>
+        <x:v>TRY-00572</x:v>
       </x:c>
       <x:c r="B115" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -4745,7 +4745,7 @@
     </x:row>
     <x:row r="116">
       <x:c r="A116" s="37" t="str">
-        <x:v>TRY-00555</x:v>
+        <x:v>TRY-00573</x:v>
       </x:c>
       <x:c r="B116" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -4782,7 +4782,7 @@
     </x:row>
     <x:row r="117">
       <x:c r="A117" s="37" t="str">
-        <x:v>TRY-00556</x:v>
+        <x:v>TRY-00574</x:v>
       </x:c>
       <x:c r="B117" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -4819,7 +4819,7 @@
     </x:row>
     <x:row r="118">
       <x:c r="A118" s="37" t="str">
-        <x:v>TRY-00557</x:v>
+        <x:v>TRY-00575</x:v>
       </x:c>
       <x:c r="B118" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -4856,7 +4856,7 @@
     </x:row>
     <x:row r="119">
       <x:c r="A119" s="37" t="str">
-        <x:v>TRY-00558</x:v>
+        <x:v>TRY-00576</x:v>
       </x:c>
       <x:c r="B119" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -4893,7 +4893,7 @@
     </x:row>
     <x:row r="120">
       <x:c r="A120" s="37" t="str">
-        <x:v>TRY-00559</x:v>
+        <x:v>TRY-00577</x:v>
       </x:c>
       <x:c r="B120" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -4930,7 +4930,7 @@
     </x:row>
     <x:row r="121">
       <x:c r="A121" s="37" t="str">
-        <x:v>TRY-00560</x:v>
+        <x:v>TRY-00578</x:v>
       </x:c>
       <x:c r="B121" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -4967,7 +4967,7 @@
     </x:row>
     <x:row r="122">
       <x:c r="A122" s="37" t="str">
-        <x:v>TRY-00561</x:v>
+        <x:v>TRY-00579</x:v>
       </x:c>
       <x:c r="B122" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -5004,7 +5004,7 @@
     </x:row>
     <x:row r="123">
       <x:c r="A123" s="37" t="str">
-        <x:v>TRY-00562</x:v>
+        <x:v>TRY-00580</x:v>
       </x:c>
       <x:c r="B123" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -5041,7 +5041,7 @@
     </x:row>
     <x:row r="124">
       <x:c r="A124" s="37" t="str">
-        <x:v>TRY-00563</x:v>
+        <x:v>TRY-00581</x:v>
       </x:c>
       <x:c r="B124" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -5078,7 +5078,7 @@
     </x:row>
     <x:row r="125">
       <x:c r="A125" s="37" t="str">
-        <x:v>TRY-00564</x:v>
+        <x:v>TRY-00582</x:v>
       </x:c>
       <x:c r="B125" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -5115,7 +5115,7 @@
     </x:row>
     <x:row r="126">
       <x:c r="A126" s="37" t="str">
-        <x:v>TRY-00565</x:v>
+        <x:v>TRY-00583</x:v>
       </x:c>
       <x:c r="B126" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -5152,7 +5152,7 @@
     </x:row>
     <x:row r="127">
       <x:c r="A127" s="37" t="str">
-        <x:v>TRY-00566</x:v>
+        <x:v>TRY-00584</x:v>
       </x:c>
       <x:c r="B127" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -5189,7 +5189,7 @@
     </x:row>
     <x:row r="128">
       <x:c r="A128" s="37" t="str">
-        <x:v>TRY-00567</x:v>
+        <x:v>TRY-00585</x:v>
       </x:c>
       <x:c r="B128" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -5226,7 +5226,7 @@
     </x:row>
     <x:row r="129">
       <x:c r="A129" s="37" t="str">
-        <x:v>TRY-00568</x:v>
+        <x:v>TRY-00586</x:v>
       </x:c>
       <x:c r="B129" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -5263,7 +5263,7 @@
     </x:row>
     <x:row r="130">
       <x:c r="A130" s="37" t="str">
-        <x:v>TRY-00569</x:v>
+        <x:v>TRY-00587</x:v>
       </x:c>
       <x:c r="B130" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -5300,7 +5300,7 @@
     </x:row>
     <x:row r="131">
       <x:c r="A131" s="37" t="str">
-        <x:v>TRY-00570</x:v>
+        <x:v>TRY-00588</x:v>
       </x:c>
       <x:c r="B131" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -5337,7 +5337,7 @@
     </x:row>
     <x:row r="132">
       <x:c r="A132" s="37" t="str">
-        <x:v>TRY-00571</x:v>
+        <x:v>TRY-00589</x:v>
       </x:c>
       <x:c r="B132" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -5374,7 +5374,7 @@
     </x:row>
     <x:row r="133">
       <x:c r="A133" s="37" t="str">
-        <x:v>TRY-00572</x:v>
+        <x:v>TRY-00590</x:v>
       </x:c>
       <x:c r="B133" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -5411,7 +5411,7 @@
     </x:row>
     <x:row r="134">
       <x:c r="A134" s="37" t="str">
-        <x:v>TRY-00573</x:v>
+        <x:v>TRY-00591</x:v>
       </x:c>
       <x:c r="B134" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -5448,7 +5448,7 @@
     </x:row>
     <x:row r="135">
       <x:c r="A135" s="37" t="str">
-        <x:v>TRY-00574</x:v>
+        <x:v>TRY-00592</x:v>
       </x:c>
       <x:c r="B135" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -5485,7 +5485,7 @@
     </x:row>
     <x:row r="136">
       <x:c r="A136" s="37" t="str">
-        <x:v>TRY-00575</x:v>
+        <x:v>TRY-00593</x:v>
       </x:c>
       <x:c r="B136" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -5522,7 +5522,7 @@
     </x:row>
     <x:row r="137">
       <x:c r="A137" s="37" t="str">
-        <x:v>TRY-00576</x:v>
+        <x:v>TRY-00594</x:v>
       </x:c>
       <x:c r="B137" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -5559,7 +5559,7 @@
     </x:row>
     <x:row r="138">
       <x:c r="A138" s="37" t="str">
-        <x:v>TRY-00577</x:v>
+        <x:v>TRY-00595</x:v>
       </x:c>
       <x:c r="B138" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -5596,7 +5596,7 @@
     </x:row>
     <x:row r="139">
       <x:c r="A139" s="37" t="str">
-        <x:v>TRY-00578</x:v>
+        <x:v>TRY-00596</x:v>
       </x:c>
       <x:c r="B139" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -5633,7 +5633,7 @@
     </x:row>
     <x:row r="140">
       <x:c r="A140" s="37" t="str">
-        <x:v>TRY-00579</x:v>
+        <x:v>TRY-00597</x:v>
       </x:c>
       <x:c r="B140" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -5670,7 +5670,7 @@
     </x:row>
     <x:row r="141">
       <x:c r="A141" s="37" t="str">
-        <x:v>TRY-00580</x:v>
+        <x:v>TRY-00598</x:v>
       </x:c>
       <x:c r="B141" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -5707,7 +5707,7 @@
     </x:row>
     <x:row r="142">
       <x:c r="A142" s="37" t="str">
-        <x:v>TRY-00581</x:v>
+        <x:v>TRY-00599</x:v>
       </x:c>
       <x:c r="B142" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -5744,7 +5744,7 @@
     </x:row>
     <x:row r="143">
       <x:c r="A143" s="37" t="str">
-        <x:v>TRY-00582</x:v>
+        <x:v>TRY-00600</x:v>
       </x:c>
       <x:c r="B143" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -5781,7 +5781,7 @@
     </x:row>
     <x:row r="144">
       <x:c r="A144" s="37" t="str">
-        <x:v>TRY-00583</x:v>
+        <x:v>TRY-00601</x:v>
       </x:c>
       <x:c r="B144" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -5818,7 +5818,7 @@
     </x:row>
     <x:row r="145">
       <x:c r="A145" s="37" t="str">
-        <x:v>TRY-00584</x:v>
+        <x:v>TRY-00602</x:v>
       </x:c>
       <x:c r="B145" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -5855,7 +5855,7 @@
     </x:row>
     <x:row r="146">
       <x:c r="A146" s="37" t="str">
-        <x:v>TRY-00585</x:v>
+        <x:v>TRY-00603</x:v>
       </x:c>
       <x:c r="B146" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -5892,7 +5892,7 @@
     </x:row>
     <x:row r="147">
       <x:c r="A147" s="37" t="str">
-        <x:v>TRY-00586</x:v>
+        <x:v>TRY-00604</x:v>
       </x:c>
       <x:c r="B147" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -5929,7 +5929,7 @@
     </x:row>
     <x:row r="148">
       <x:c r="A148" s="37" t="str">
-        <x:v>TRY-00587</x:v>
+        <x:v>TRY-00605</x:v>
       </x:c>
       <x:c r="B148" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -5966,7 +5966,7 @@
     </x:row>
     <x:row r="149">
       <x:c r="A149" s="37" t="str">
-        <x:v>TRY-00588</x:v>
+        <x:v>TRY-00606</x:v>
       </x:c>
       <x:c r="B149" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -6003,7 +6003,7 @@
     </x:row>
     <x:row r="150">
       <x:c r="A150" s="37" t="str">
-        <x:v>TRY-00589</x:v>
+        <x:v>TRY-00607</x:v>
       </x:c>
       <x:c r="B150" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -6040,7 +6040,7 @@
     </x:row>
     <x:row r="151">
       <x:c r="A151" s="37" t="str">
-        <x:v>TRY-00590</x:v>
+        <x:v>TRY-00608</x:v>
       </x:c>
       <x:c r="B151" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -6077,7 +6077,7 @@
     </x:row>
     <x:row r="152">
       <x:c r="A152" s="37" t="str">
-        <x:v>TRY-00591</x:v>
+        <x:v>TRY-00609</x:v>
       </x:c>
       <x:c r="B152" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -6114,7 +6114,7 @@
     </x:row>
     <x:row r="153">
       <x:c r="A153" s="37" t="str">
-        <x:v>TRY-00592</x:v>
+        <x:v>TRY-00610</x:v>
       </x:c>
       <x:c r="B153" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -6151,7 +6151,7 @@
     </x:row>
     <x:row r="154">
       <x:c r="A154" s="37" t="str">
-        <x:v>TRY-00797</x:v>
+        <x:v>TRY-00815</x:v>
       </x:c>
       <x:c r="B154" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -6188,7 +6188,7 @@
     </x:row>
     <x:row r="155">
       <x:c r="A155" s="37" t="str">
-        <x:v>TRY-00798</x:v>
+        <x:v>TRY-00816</x:v>
       </x:c>
       <x:c r="B155" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -6225,7 +6225,7 @@
     </x:row>
     <x:row r="156">
       <x:c r="A156" s="37" t="str">
-        <x:v>TRY-00799</x:v>
+        <x:v>TRY-00817</x:v>
       </x:c>
       <x:c r="B156" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -6262,7 +6262,7 @@
     </x:row>
     <x:row r="157">
       <x:c r="A157" s="37" t="str">
-        <x:v>TRY-00800</x:v>
+        <x:v>TRY-00818</x:v>
       </x:c>
       <x:c r="B157" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -6299,7 +6299,7 @@
     </x:row>
     <x:row r="158">
       <x:c r="A158" s="37" t="str">
-        <x:v>TRY-00801</x:v>
+        <x:v>TRY-00819</x:v>
       </x:c>
       <x:c r="B158" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -6336,7 +6336,7 @@
     </x:row>
     <x:row r="159">
       <x:c r="A159" s="37" t="str">
-        <x:v>TRY-00802</x:v>
+        <x:v>TRY-00820</x:v>
       </x:c>
       <x:c r="B159" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -6373,7 +6373,7 @@
     </x:row>
     <x:row r="160">
       <x:c r="A160" s="37" t="str">
-        <x:v>TRY-00803</x:v>
+        <x:v>TRY-00821</x:v>
       </x:c>
       <x:c r="B160" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -6410,7 +6410,7 @@
     </x:row>
     <x:row r="161">
       <x:c r="A161" s="37" t="str">
-        <x:v>TRY-00804</x:v>
+        <x:v>TRY-00822</x:v>
       </x:c>
       <x:c r="B161" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -6447,7 +6447,7 @@
     </x:row>
     <x:row r="162">
       <x:c r="A162" s="37" t="str">
-        <x:v>TRY-00805</x:v>
+        <x:v>TRY-00823</x:v>
       </x:c>
       <x:c r="B162" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -6484,7 +6484,7 @@
     </x:row>
     <x:row r="163">
       <x:c r="A163" s="37" t="str">
-        <x:v>TRY-00806</x:v>
+        <x:v>TRY-00824</x:v>
       </x:c>
       <x:c r="B163" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -6521,7 +6521,7 @@
     </x:row>
     <x:row r="164">
       <x:c r="A164" s="37" t="str">
-        <x:v>TRY-00807</x:v>
+        <x:v>TRY-00825</x:v>
       </x:c>
       <x:c r="B164" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -6558,7 +6558,7 @@
     </x:row>
     <x:row r="165">
       <x:c r="A165" s="37" t="str">
-        <x:v>TRY-00808</x:v>
+        <x:v>TRY-00826</x:v>
       </x:c>
       <x:c r="B165" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -6595,7 +6595,7 @@
     </x:row>
     <x:row r="166">
       <x:c r="A166" s="37" t="str">
-        <x:v>TRY-00809</x:v>
+        <x:v>TRY-00827</x:v>
       </x:c>
       <x:c r="B166" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -6632,7 +6632,7 @@
     </x:row>
     <x:row r="167">
       <x:c r="A167" s="37" t="str">
-        <x:v>TRY-00810</x:v>
+        <x:v>TRY-00828</x:v>
       </x:c>
       <x:c r="B167" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -6669,7 +6669,7 @@
     </x:row>
     <x:row r="168">
       <x:c r="A168" s="37" t="str">
-        <x:v>TRY-00811</x:v>
+        <x:v>TRY-00829</x:v>
       </x:c>
       <x:c r="B168" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -6706,7 +6706,7 @@
     </x:row>
     <x:row r="169">
       <x:c r="A169" s="37" t="str">
-        <x:v>TRY-00812</x:v>
+        <x:v>TRY-00830</x:v>
       </x:c>
       <x:c r="B169" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -6743,7 +6743,7 @@
     </x:row>
     <x:row r="170">
       <x:c r="A170" s="37" t="str">
-        <x:v>TRY-00813</x:v>
+        <x:v>TRY-00831</x:v>
       </x:c>
       <x:c r="B170" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -6780,7 +6780,7 @@
     </x:row>
     <x:row r="171">
       <x:c r="A171" s="37" t="str">
-        <x:v>TRY-00814</x:v>
+        <x:v>TRY-00832</x:v>
       </x:c>
       <x:c r="B171" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -6817,7 +6817,7 @@
     </x:row>
     <x:row r="172">
       <x:c r="A172" s="37" t="str">
-        <x:v>TRY-00815</x:v>
+        <x:v>TRY-00833</x:v>
       </x:c>
       <x:c r="B172" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -6854,7 +6854,7 @@
     </x:row>
     <x:row r="173">
       <x:c r="A173" s="37" t="str">
-        <x:v>TRY-00816</x:v>
+        <x:v>TRY-00834</x:v>
       </x:c>
       <x:c r="B173" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -6891,7 +6891,7 @@
     </x:row>
     <x:row r="174">
       <x:c r="A174" s="37" t="str">
-        <x:v>TRY-00817</x:v>
+        <x:v>TRY-00835</x:v>
       </x:c>
       <x:c r="B174" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -6928,7 +6928,7 @@
     </x:row>
     <x:row r="175">
       <x:c r="A175" s="37" t="str">
-        <x:v>TRY-00818</x:v>
+        <x:v>TRY-00836</x:v>
       </x:c>
       <x:c r="B175" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -6965,7 +6965,7 @@
     </x:row>
     <x:row r="176">
       <x:c r="A176" s="37" t="str">
-        <x:v>TRY-00819</x:v>
+        <x:v>TRY-00837</x:v>
       </x:c>
       <x:c r="B176" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -7002,7 +7002,7 @@
     </x:row>
     <x:row r="177">
       <x:c r="A177" s="37" t="str">
-        <x:v>TRY-00820</x:v>
+        <x:v>TRY-00838</x:v>
       </x:c>
       <x:c r="B177" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -7039,7 +7039,7 @@
     </x:row>
     <x:row r="178">
       <x:c r="A178" s="37" t="str">
-        <x:v>TRY-00821</x:v>
+        <x:v>TRY-00839</x:v>
       </x:c>
       <x:c r="B178" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -7076,7 +7076,7 @@
     </x:row>
     <x:row r="179">
       <x:c r="A179" s="37" t="str">
-        <x:v>TRY-00822</x:v>
+        <x:v>TRY-00840</x:v>
       </x:c>
       <x:c r="B179" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -7113,7 +7113,7 @@
     </x:row>
     <x:row r="180">
       <x:c r="A180" s="37" t="str">
-        <x:v>TRY-00823</x:v>
+        <x:v>TRY-00841</x:v>
       </x:c>
       <x:c r="B180" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -7150,7 +7150,7 @@
     </x:row>
     <x:row r="181">
       <x:c r="A181" s="37" t="str">
-        <x:v>TRY-00824</x:v>
+        <x:v>TRY-00842</x:v>
       </x:c>
       <x:c r="B181" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -7187,7 +7187,7 @@
     </x:row>
     <x:row r="182">
       <x:c r="A182" s="37" t="str">
-        <x:v>TRY-00825</x:v>
+        <x:v>TRY-00843</x:v>
       </x:c>
       <x:c r="B182" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -7224,7 +7224,7 @@
     </x:row>
     <x:row r="183">
       <x:c r="A183" s="37" t="str">
-        <x:v>TRY-00826</x:v>
+        <x:v>TRY-00844</x:v>
       </x:c>
       <x:c r="B183" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -7261,7 +7261,7 @@
     </x:row>
     <x:row r="184">
       <x:c r="A184" s="37" t="str">
-        <x:v>TRY-00827</x:v>
+        <x:v>TRY-00845</x:v>
       </x:c>
       <x:c r="B184" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -7298,7 +7298,7 @@
     </x:row>
     <x:row r="185">
       <x:c r="A185" s="37" t="str">
-        <x:v>TRY-00828</x:v>
+        <x:v>TRY-00846</x:v>
       </x:c>
       <x:c r="B185" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -7335,7 +7335,7 @@
     </x:row>
     <x:row r="186">
       <x:c r="A186" s="37" t="str">
-        <x:v>TRY-00829</x:v>
+        <x:v>TRY-00847</x:v>
       </x:c>
       <x:c r="B186" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -7372,7 +7372,7 @@
     </x:row>
     <x:row r="187">
       <x:c r="A187" s="37" t="str">
-        <x:v>TRY-00830</x:v>
+        <x:v>TRY-00848</x:v>
       </x:c>
       <x:c r="B187" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -7409,7 +7409,7 @@
     </x:row>
     <x:row r="188">
       <x:c r="A188" s="37" t="str">
-        <x:v>TRY-00831</x:v>
+        <x:v>TRY-00849</x:v>
       </x:c>
       <x:c r="B188" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -7446,7 +7446,7 @@
     </x:row>
     <x:row r="189">
       <x:c r="A189" s="37" t="str">
-        <x:v>TRY-00832</x:v>
+        <x:v>TRY-00850</x:v>
       </x:c>
       <x:c r="B189" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -7483,7 +7483,7 @@
     </x:row>
     <x:row r="190">
       <x:c r="A190" s="37" t="str">
-        <x:v>TRY-00833</x:v>
+        <x:v>TRY-00851</x:v>
       </x:c>
       <x:c r="B190" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -7520,7 +7520,7 @@
     </x:row>
     <x:row r="191">
       <x:c r="A191" s="37" t="str">
-        <x:v>TRY-00834</x:v>
+        <x:v>TRY-00852</x:v>
       </x:c>
       <x:c r="B191" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -7557,7 +7557,7 @@
     </x:row>
     <x:row r="192">
       <x:c r="A192" s="37" t="str">
-        <x:v>TRY-00847</x:v>
+        <x:v>TRY-00865</x:v>
       </x:c>
       <x:c r="B192" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -7594,7 +7594,7 @@
     </x:row>
     <x:row r="193">
       <x:c r="A193" s="37" t="str">
-        <x:v>TRY-00848</x:v>
+        <x:v>TRY-00866</x:v>
       </x:c>
       <x:c r="B193" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -7631,7 +7631,7 @@
     </x:row>
     <x:row r="194">
       <x:c r="A194" s="37" t="str">
-        <x:v>TRY-00849</x:v>
+        <x:v>TRY-00867</x:v>
       </x:c>
       <x:c r="B194" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -7668,7 +7668,7 @@
     </x:row>
     <x:row r="195">
       <x:c r="A195" s="37" t="str">
-        <x:v>TRY-00850</x:v>
+        <x:v>TRY-00868</x:v>
       </x:c>
       <x:c r="B195" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -7705,7 +7705,7 @@
     </x:row>
     <x:row r="196">
       <x:c r="A196" s="37" t="str">
-        <x:v>TRY-00851</x:v>
+        <x:v>TRY-00869</x:v>
       </x:c>
       <x:c r="B196" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -7742,7 +7742,7 @@
     </x:row>
     <x:row r="197">
       <x:c r="A197" s="37" t="str">
-        <x:v>TRY-00852</x:v>
+        <x:v>TRY-00870</x:v>
       </x:c>
       <x:c r="B197" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -7779,7 +7779,7 @@
     </x:row>
     <x:row r="198">
       <x:c r="A198" s="37" t="str">
-        <x:v>TRY-00853</x:v>
+        <x:v>TRY-00871</x:v>
       </x:c>
       <x:c r="B198" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -7816,7 +7816,7 @@
     </x:row>
     <x:row r="199">
       <x:c r="A199" s="37" t="str">
-        <x:v>TRY-00854</x:v>
+        <x:v>TRY-00872</x:v>
       </x:c>
       <x:c r="B199" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -7853,7 +7853,7 @@
     </x:row>
     <x:row r="200">
       <x:c r="A200" s="37" t="str">
-        <x:v>TRY-00855</x:v>
+        <x:v>TRY-00873</x:v>
       </x:c>
       <x:c r="B200" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -7890,7 +7890,7 @@
     </x:row>
     <x:row r="201">
       <x:c r="A201" s="37" t="str">
-        <x:v>TRY-00856</x:v>
+        <x:v>TRY-00874</x:v>
       </x:c>
       <x:c r="B201" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -7927,7 +7927,7 @@
     </x:row>
     <x:row r="202">
       <x:c r="A202" s="37" t="str">
-        <x:v>TRY-00857</x:v>
+        <x:v>TRY-00875</x:v>
       </x:c>
       <x:c r="B202" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -7964,7 +7964,7 @@
     </x:row>
     <x:row r="203">
       <x:c r="A203" s="37" t="str">
-        <x:v>TRY-00858</x:v>
+        <x:v>TRY-00876</x:v>
       </x:c>
       <x:c r="B203" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -8001,7 +8001,7 @@
     </x:row>
     <x:row r="204">
       <x:c r="A204" s="37" t="str">
-        <x:v>TRY-00859</x:v>
+        <x:v>TRY-00877</x:v>
       </x:c>
       <x:c r="B204" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -8038,7 +8038,7 @@
     </x:row>
     <x:row r="205">
       <x:c r="A205" s="37" t="str">
-        <x:v>TRY-00860</x:v>
+        <x:v>TRY-00878</x:v>
       </x:c>
       <x:c r="B205" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -8075,7 +8075,7 @@
     </x:row>
     <x:row r="206">
       <x:c r="A206" s="37" t="str">
-        <x:v>TRY-00861</x:v>
+        <x:v>TRY-00879</x:v>
       </x:c>
       <x:c r="B206" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -8112,7 +8112,7 @@
     </x:row>
     <x:row r="207">
       <x:c r="A207" s="37" t="str">
-        <x:v>TRY-00862</x:v>
+        <x:v>TRY-00880</x:v>
       </x:c>
       <x:c r="B207" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -8149,7 +8149,7 @@
     </x:row>
     <x:row r="208">
       <x:c r="A208" s="37" t="str">
-        <x:v>TRY-00863</x:v>
+        <x:v>TRY-00881</x:v>
       </x:c>
       <x:c r="B208" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -8186,7 +8186,7 @@
     </x:row>
     <x:row r="209">
       <x:c r="A209" s="37" t="str">
-        <x:v>TRY-00864</x:v>
+        <x:v>TRY-00882</x:v>
       </x:c>
       <x:c r="B209" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -8223,7 +8223,7 @@
     </x:row>
     <x:row r="210">
       <x:c r="A210" s="37" t="str">
-        <x:v>TRY-00865</x:v>
+        <x:v>TRY-00883</x:v>
       </x:c>
       <x:c r="B210" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -8260,7 +8260,7 @@
     </x:row>
     <x:row r="211">
       <x:c r="A211" s="37" t="str">
-        <x:v>TRY-00866</x:v>
+        <x:v>TRY-00884</x:v>
       </x:c>
       <x:c r="B211" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -8297,7 +8297,7 @@
     </x:row>
     <x:row r="212">
       <x:c r="A212" s="38" t="str">
-        <x:v>TRY-00867</x:v>
+        <x:v>TRY-00885</x:v>
       </x:c>
       <x:c r="B212" s="29" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -10334,7 +10334,7 @@
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="37" t="str">
-        <x:v>TRY-00601</x:v>
+        <x:v>TRY-00619</x:v>
       </x:c>
       <x:c r="B56" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -10371,7 +10371,7 @@
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="37" t="str">
-        <x:v>TRY-00602</x:v>
+        <x:v>TRY-00620</x:v>
       </x:c>
       <x:c r="B57" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -10408,7 +10408,7 @@
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="37" t="str">
-        <x:v>TRY-00603</x:v>
+        <x:v>TRY-00621</x:v>
       </x:c>
       <x:c r="B58" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -10445,7 +10445,7 @@
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="37" t="str">
-        <x:v>TRY-00604</x:v>
+        <x:v>TRY-00622</x:v>
       </x:c>
       <x:c r="B59" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -10482,7 +10482,7 @@
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="37" t="str">
-        <x:v>TRY-00605</x:v>
+        <x:v>TRY-00623</x:v>
       </x:c>
       <x:c r="B60" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -10519,7 +10519,7 @@
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="37" t="str">
-        <x:v>TRY-00606</x:v>
+        <x:v>TRY-00624</x:v>
       </x:c>
       <x:c r="B61" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -10556,7 +10556,7 @@
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="37" t="str">
-        <x:v>TRY-00607</x:v>
+        <x:v>TRY-00625</x:v>
       </x:c>
       <x:c r="B62" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -10593,7 +10593,7 @@
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="37" t="str">
-        <x:v>TRY-00608</x:v>
+        <x:v>TRY-00626</x:v>
       </x:c>
       <x:c r="B63" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -10630,7 +10630,7 @@
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="37" t="str">
-        <x:v>TRY-00609</x:v>
+        <x:v>TRY-00627</x:v>
       </x:c>
       <x:c r="B64" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -10667,7 +10667,7 @@
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="37" t="str">
-        <x:v>TRY-00610</x:v>
+        <x:v>TRY-00628</x:v>
       </x:c>
       <x:c r="B65" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -10704,7 +10704,7 @@
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="37" t="str">
-        <x:v>TRY-00611</x:v>
+        <x:v>TRY-00629</x:v>
       </x:c>
       <x:c r="B66" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -10741,7 +10741,7 @@
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="37" t="str">
-        <x:v>TRY-00612</x:v>
+        <x:v>TRY-00630</x:v>
       </x:c>
       <x:c r="B67" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -10778,7 +10778,7 @@
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="37" t="str">
-        <x:v>TRY-00613</x:v>
+        <x:v>TRY-00631</x:v>
       </x:c>
       <x:c r="B68" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -10815,7 +10815,7 @@
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="37" t="str">
-        <x:v>TRY-00614</x:v>
+        <x:v>TRY-00632</x:v>
       </x:c>
       <x:c r="B69" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -10852,7 +10852,7 @@
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="37" t="str">
-        <x:v>TRY-00615</x:v>
+        <x:v>TRY-00633</x:v>
       </x:c>
       <x:c r="B70" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -10889,7 +10889,7 @@
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="37" t="str">
-        <x:v>TRY-00616</x:v>
+        <x:v>TRY-00634</x:v>
       </x:c>
       <x:c r="B71" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -10926,7 +10926,7 @@
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="37" t="str">
-        <x:v>TRY-00617</x:v>
+        <x:v>TRY-00635</x:v>
       </x:c>
       <x:c r="B72" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -10963,7 +10963,7 @@
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="37" t="str">
-        <x:v>TRY-00618</x:v>
+        <x:v>TRY-00636</x:v>
       </x:c>
       <x:c r="B73" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -11000,7 +11000,7 @@
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="37" t="str">
-        <x:v>TRY-00619</x:v>
+        <x:v>TRY-00637</x:v>
       </x:c>
       <x:c r="B74" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -11037,7 +11037,7 @@
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="37" t="str">
-        <x:v>TRY-00620</x:v>
+        <x:v>TRY-00638</x:v>
       </x:c>
       <x:c r="B75" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -11074,7 +11074,7 @@
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="37" t="str">
-        <x:v>TRY-00621</x:v>
+        <x:v>TRY-00639</x:v>
       </x:c>
       <x:c r="B76" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -11111,7 +11111,7 @@
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="37" t="str">
-        <x:v>TRY-00622</x:v>
+        <x:v>TRY-00640</x:v>
       </x:c>
       <x:c r="B77" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -11148,7 +11148,7 @@
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="37" t="str">
-        <x:v>TRY-00623</x:v>
+        <x:v>TRY-00641</x:v>
       </x:c>
       <x:c r="B78" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -11185,7 +11185,7 @@
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="37" t="str">
-        <x:v>TRY-00624</x:v>
+        <x:v>TRY-00642</x:v>
       </x:c>
       <x:c r="B79" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -11222,7 +11222,7 @@
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="37" t="str">
-        <x:v>TRY-00625</x:v>
+        <x:v>TRY-00643</x:v>
       </x:c>
       <x:c r="B80" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -11259,7 +11259,7 @@
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="37" t="str">
-        <x:v>TRY-00626</x:v>
+        <x:v>TRY-00644</x:v>
       </x:c>
       <x:c r="B81" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -11296,7 +11296,7 @@
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="37" t="str">
-        <x:v>TRY-00627</x:v>
+        <x:v>TRY-00645</x:v>
       </x:c>
       <x:c r="B82" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -11333,7 +11333,7 @@
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="37" t="str">
-        <x:v>TRY-00628</x:v>
+        <x:v>TRY-00646</x:v>
       </x:c>
       <x:c r="B83" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -11370,7 +11370,7 @@
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="37" t="str">
-        <x:v>TRY-00629</x:v>
+        <x:v>TRY-00647</x:v>
       </x:c>
       <x:c r="B84" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -11407,7 +11407,7 @@
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="37" t="str">
-        <x:v>TRY-00630</x:v>
+        <x:v>TRY-00648</x:v>
       </x:c>
       <x:c r="B85" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -11444,7 +11444,7 @@
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="37" t="str">
-        <x:v>TRY-00631</x:v>
+        <x:v>TRY-00649</x:v>
       </x:c>
       <x:c r="B86" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -11481,7 +11481,7 @@
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="37" t="str">
-        <x:v>TRY-00632</x:v>
+        <x:v>TRY-00650</x:v>
       </x:c>
       <x:c r="B87" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -11518,7 +11518,7 @@
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="37" t="str">
-        <x:v>TRY-00647</x:v>
+        <x:v>TRY-00665</x:v>
       </x:c>
       <x:c r="B88" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -11555,7 +11555,7 @@
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="37" t="str">
-        <x:v>TRY-00648</x:v>
+        <x:v>TRY-00666</x:v>
       </x:c>
       <x:c r="B89" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -11592,7 +11592,7 @@
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="37" t="str">
-        <x:v>TRY-00649</x:v>
+        <x:v>TRY-00667</x:v>
       </x:c>
       <x:c r="B90" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -11629,7 +11629,7 @@
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="37" t="str">
-        <x:v>TRY-00650</x:v>
+        <x:v>TRY-00668</x:v>
       </x:c>
       <x:c r="B91" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -11666,7 +11666,7 @@
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="37" t="str">
-        <x:v>TRY-00651</x:v>
+        <x:v>TRY-00669</x:v>
       </x:c>
       <x:c r="B92" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -11703,7 +11703,7 @@
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="37" t="str">
-        <x:v>TRY-00652</x:v>
+        <x:v>TRY-00670</x:v>
       </x:c>
       <x:c r="B93" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -11740,7 +11740,7 @@
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="37" t="str">
-        <x:v>TRY-00653</x:v>
+        <x:v>TRY-00671</x:v>
       </x:c>
       <x:c r="B94" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -11777,7 +11777,7 @@
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="37" t="str">
-        <x:v>TRY-00654</x:v>
+        <x:v>TRY-00672</x:v>
       </x:c>
       <x:c r="B95" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -11814,7 +11814,7 @@
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="37" t="str">
-        <x:v>TRY-00655</x:v>
+        <x:v>TRY-00673</x:v>
       </x:c>
       <x:c r="B96" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -11851,7 +11851,7 @@
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="37" t="str">
-        <x:v>TRY-00656</x:v>
+        <x:v>TRY-00674</x:v>
       </x:c>
       <x:c r="B97" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -11888,7 +11888,7 @@
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="37" t="str">
-        <x:v>TRY-00657</x:v>
+        <x:v>TRY-00675</x:v>
       </x:c>
       <x:c r="B98" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -11925,7 +11925,7 @@
     </x:row>
     <x:row r="99">
       <x:c r="A99" s="37" t="str">
-        <x:v>TRY-00658</x:v>
+        <x:v>TRY-00676</x:v>
       </x:c>
       <x:c r="B99" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -11962,7 +11962,7 @@
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="37" t="str">
-        <x:v>TRY-00659</x:v>
+        <x:v>TRY-00677</x:v>
       </x:c>
       <x:c r="B100" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -11999,7 +11999,7 @@
     </x:row>
     <x:row r="101">
       <x:c r="A101" s="37" t="str">
-        <x:v>TRY-00666</x:v>
+        <x:v>TRY-00684</x:v>
       </x:c>
       <x:c r="B101" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -12036,7 +12036,7 @@
     </x:row>
     <x:row r="102">
       <x:c r="A102" s="37" t="str">
-        <x:v>TRY-00667</x:v>
+        <x:v>TRY-00685</x:v>
       </x:c>
       <x:c r="B102" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -12073,7 +12073,7 @@
     </x:row>
     <x:row r="103">
       <x:c r="A103" s="37" t="str">
-        <x:v>TRY-00668</x:v>
+        <x:v>TRY-00686</x:v>
       </x:c>
       <x:c r="B103" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -12110,7 +12110,7 @@
     </x:row>
     <x:row r="104">
       <x:c r="A104" s="37" t="str">
-        <x:v>TRY-00669</x:v>
+        <x:v>TRY-00687</x:v>
       </x:c>
       <x:c r="B104" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -12147,7 +12147,7 @@
     </x:row>
     <x:row r="105">
       <x:c r="A105" s="37" t="str">
-        <x:v>TRY-00670</x:v>
+        <x:v>TRY-00688</x:v>
       </x:c>
       <x:c r="B105" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -12184,7 +12184,7 @@
     </x:row>
     <x:row r="106">
       <x:c r="A106" s="37" t="str">
-        <x:v>TRY-00671</x:v>
+        <x:v>TRY-00689</x:v>
       </x:c>
       <x:c r="B106" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -12221,7 +12221,7 @@
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="37" t="str">
-        <x:v>TRY-00672</x:v>
+        <x:v>TRY-00690</x:v>
       </x:c>
       <x:c r="B107" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -12258,7 +12258,7 @@
     </x:row>
     <x:row r="108">
       <x:c r="A108" s="37" t="str">
-        <x:v>TRY-00673</x:v>
+        <x:v>TRY-00691</x:v>
       </x:c>
       <x:c r="B108" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -12295,7 +12295,7 @@
     </x:row>
     <x:row r="109">
       <x:c r="A109" s="37" t="str">
-        <x:v>TRY-00674</x:v>
+        <x:v>TRY-00692</x:v>
       </x:c>
       <x:c r="B109" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -12332,7 +12332,7 @@
     </x:row>
     <x:row r="110">
       <x:c r="A110" s="37" t="str">
-        <x:v>TRY-00675</x:v>
+        <x:v>TRY-00693</x:v>
       </x:c>
       <x:c r="B110" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -12369,7 +12369,7 @@
     </x:row>
     <x:row r="111">
       <x:c r="A111" s="37" t="str">
-        <x:v>TRY-00676</x:v>
+        <x:v>TRY-00694</x:v>
       </x:c>
       <x:c r="B111" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -12406,7 +12406,7 @@
     </x:row>
     <x:row r="112">
       <x:c r="A112" s="37" t="str">
-        <x:v>TRY-00677</x:v>
+        <x:v>TRY-00695</x:v>
       </x:c>
       <x:c r="B112" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -12443,7 +12443,7 @@
     </x:row>
     <x:row r="113">
       <x:c r="A113" s="37" t="str">
-        <x:v>TRY-00678</x:v>
+        <x:v>TRY-00696</x:v>
       </x:c>
       <x:c r="B113" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -12480,7 +12480,7 @@
     </x:row>
     <x:row r="114">
       <x:c r="A114" s="37" t="str">
-        <x:v>TRY-00679</x:v>
+        <x:v>TRY-00697</x:v>
       </x:c>
       <x:c r="B114" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -12517,7 +12517,7 @@
     </x:row>
     <x:row r="115">
       <x:c r="A115" s="37" t="str">
-        <x:v>TRY-00680</x:v>
+        <x:v>TRY-00698</x:v>
       </x:c>
       <x:c r="B115" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -12554,7 +12554,7 @@
     </x:row>
     <x:row r="116">
       <x:c r="A116" s="37" t="str">
-        <x:v>TRY-00681</x:v>
+        <x:v>TRY-00699</x:v>
       </x:c>
       <x:c r="B116" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -12591,7 +12591,7 @@
     </x:row>
     <x:row r="117">
       <x:c r="A117" s="37" t="str">
-        <x:v>TRY-00682</x:v>
+        <x:v>TRY-00700</x:v>
       </x:c>
       <x:c r="B117" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -12628,7 +12628,7 @@
     </x:row>
     <x:row r="118">
       <x:c r="A118" s="37" t="str">
-        <x:v>TRY-00683</x:v>
+        <x:v>TRY-00701</x:v>
       </x:c>
       <x:c r="B118" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -12665,7 +12665,7 @@
     </x:row>
     <x:row r="119">
       <x:c r="A119" s="37" t="str">
-        <x:v>TRY-00684</x:v>
+        <x:v>TRY-00702</x:v>
       </x:c>
       <x:c r="B119" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -12702,7 +12702,7 @@
     </x:row>
     <x:row r="120">
       <x:c r="A120" s="37" t="str">
-        <x:v>TRY-00685</x:v>
+        <x:v>TRY-00703</x:v>
       </x:c>
       <x:c r="B120" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -12739,7 +12739,7 @@
     </x:row>
     <x:row r="121">
       <x:c r="A121" s="37" t="str">
-        <x:v>TRY-00686</x:v>
+        <x:v>TRY-00704</x:v>
       </x:c>
       <x:c r="B121" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -12776,7 +12776,7 @@
     </x:row>
     <x:row r="122">
       <x:c r="A122" s="37" t="str">
-        <x:v>TRY-00687</x:v>
+        <x:v>TRY-00705</x:v>
       </x:c>
       <x:c r="B122" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -12813,7 +12813,7 @@
     </x:row>
     <x:row r="123">
       <x:c r="A123" s="37" t="str">
-        <x:v>TRY-00688</x:v>
+        <x:v>TRY-00706</x:v>
       </x:c>
       <x:c r="B123" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -12850,7 +12850,7 @@
     </x:row>
     <x:row r="124">
       <x:c r="A124" s="37" t="str">
-        <x:v>TRY-00689</x:v>
+        <x:v>TRY-00707</x:v>
       </x:c>
       <x:c r="B124" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -12887,7 +12887,7 @@
     </x:row>
     <x:row r="125">
       <x:c r="A125" s="37" t="str">
-        <x:v>TRY-00690</x:v>
+        <x:v>TRY-00708</x:v>
       </x:c>
       <x:c r="B125" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -12924,7 +12924,7 @@
     </x:row>
     <x:row r="126">
       <x:c r="A126" s="37" t="str">
-        <x:v>TRY-00691</x:v>
+        <x:v>TRY-00709</x:v>
       </x:c>
       <x:c r="B126" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -12961,7 +12961,7 @@
     </x:row>
     <x:row r="127">
       <x:c r="A127" s="37" t="str">
-        <x:v>TRY-00692</x:v>
+        <x:v>TRY-00710</x:v>
       </x:c>
       <x:c r="B127" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -12998,7 +12998,7 @@
     </x:row>
     <x:row r="128">
       <x:c r="A128" s="37" t="str">
-        <x:v>TRY-00693</x:v>
+        <x:v>TRY-00711</x:v>
       </x:c>
       <x:c r="B128" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -13035,7 +13035,7 @@
     </x:row>
     <x:row r="129">
       <x:c r="A129" s="37" t="str">
-        <x:v>TRY-00694</x:v>
+        <x:v>TRY-00712</x:v>
       </x:c>
       <x:c r="B129" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -13072,7 +13072,7 @@
     </x:row>
     <x:row r="130">
       <x:c r="A130" s="37" t="str">
-        <x:v>TRY-00707</x:v>
+        <x:v>TRY-00725</x:v>
       </x:c>
       <x:c r="B130" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -13109,7 +13109,7 @@
     </x:row>
     <x:row r="131">
       <x:c r="A131" s="37" t="str">
-        <x:v>TRY-00708</x:v>
+        <x:v>TRY-00726</x:v>
       </x:c>
       <x:c r="B131" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -13146,7 +13146,7 @@
     </x:row>
     <x:row r="132">
       <x:c r="A132" s="37" t="str">
-        <x:v>TRY-00709</x:v>
+        <x:v>TRY-00727</x:v>
       </x:c>
       <x:c r="B132" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -13183,7 +13183,7 @@
     </x:row>
     <x:row r="133">
       <x:c r="A133" s="37" t="str">
-        <x:v>TRY-00710</x:v>
+        <x:v>TRY-00728</x:v>
       </x:c>
       <x:c r="B133" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -13220,7 +13220,7 @@
     </x:row>
     <x:row r="134">
       <x:c r="A134" s="37" t="str">
-        <x:v>TRY-00711</x:v>
+        <x:v>TRY-00729</x:v>
       </x:c>
       <x:c r="B134" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -13257,7 +13257,7 @@
     </x:row>
     <x:row r="135">
       <x:c r="A135" s="37" t="str">
-        <x:v>TRY-00712</x:v>
+        <x:v>TRY-00730</x:v>
       </x:c>
       <x:c r="B135" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -13294,7 +13294,7 @@
     </x:row>
     <x:row r="136">
       <x:c r="A136" s="38" t="str">
-        <x:v>TRY-00713</x:v>
+        <x:v>TRY-00731</x:v>
       </x:c>
       <x:c r="B136" s="29" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -14470,7 +14470,7 @@
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="37" t="str">
-        <x:v>TRY-00448</x:v>
+        <x:v>TRY-00466</x:v>
       </x:c>
       <x:c r="B33" s="28" t="str">
         <x:v>Bank relationship profitability scorecard</x:v>
@@ -14507,7 +14507,7 @@
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="37" t="str">
-        <x:v>TRY-00449</x:v>
+        <x:v>TRY-00467</x:v>
       </x:c>
       <x:c r="B34" s="28" t="str">
         <x:v>Bank relationship profitability scorecard</x:v>
@@ -14544,7 +14544,7 @@
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="37" t="str">
-        <x:v>TRY-00450</x:v>
+        <x:v>TRY-00468</x:v>
       </x:c>
       <x:c r="B35" s="28" t="str">
         <x:v>Bank relationship profitability scorecard</x:v>
@@ -14581,7 +14581,7 @@
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="37" t="str">
-        <x:v>TRY-00451</x:v>
+        <x:v>TRY-00469</x:v>
       </x:c>
       <x:c r="B36" s="28" t="str">
         <x:v>Bank relationship profitability scorecard</x:v>
@@ -14618,7 +14618,7 @@
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="37" t="str">
-        <x:v>TRY-00452</x:v>
+        <x:v>TRY-00470</x:v>
       </x:c>
       <x:c r="B37" s="28" t="str">
         <x:v>Bank relationship profitability scorecard</x:v>
@@ -14655,7 +14655,7 @@
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="37" t="str">
-        <x:v>TRY-00453</x:v>
+        <x:v>TRY-00471</x:v>
       </x:c>
       <x:c r="B38" s="28" t="str">
         <x:v>Bank relationship profitability scorecard</x:v>
@@ -14692,7 +14692,7 @@
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="37" t="str">
-        <x:v>TRY-00454</x:v>
+        <x:v>TRY-00472</x:v>
       </x:c>
       <x:c r="B39" s="28" t="str">
         <x:v>Bank relationship profitability scorecard</x:v>
@@ -14729,7 +14729,7 @@
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="37" t="str">
-        <x:v>TRY-00455</x:v>
+        <x:v>TRY-00473</x:v>
       </x:c>
       <x:c r="B40" s="28" t="str">
         <x:v>Bank relationship profitability scorecard</x:v>
@@ -14766,7 +14766,7 @@
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="37" t="str">
-        <x:v>TRY-00456</x:v>
+        <x:v>TRY-00474</x:v>
       </x:c>
       <x:c r="B41" s="28" t="str">
         <x:v>Bank relationship profitability scorecard</x:v>
@@ -14803,7 +14803,7 @@
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="37" t="str">
-        <x:v>TRY-00457</x:v>
+        <x:v>TRY-00475</x:v>
       </x:c>
       <x:c r="B42" s="28" t="str">
         <x:v>Bank relationship profitability scorecard</x:v>
@@ -14840,7 +14840,7 @@
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="37" t="str">
-        <x:v>TRY-00458</x:v>
+        <x:v>TRY-00476</x:v>
       </x:c>
       <x:c r="B43" s="28" t="str">
         <x:v>Bank relationship profitability scorecard</x:v>
@@ -14877,7 +14877,7 @@
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="37" t="str">
-        <x:v>TRY-00459</x:v>
+        <x:v>TRY-00477</x:v>
       </x:c>
       <x:c r="B44" s="28" t="str">
         <x:v>Bank relationship profitability scorecard</x:v>
@@ -14914,7 +14914,7 @@
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="37" t="str">
-        <x:v>TRY-00460</x:v>
+        <x:v>TRY-00478</x:v>
       </x:c>
       <x:c r="B45" s="28" t="str">
         <x:v>Bank relationship profitability scorecard</x:v>
@@ -14951,7 +14951,7 @@
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="37" t="str">
-        <x:v>TRY-00461</x:v>
+        <x:v>TRY-00479</x:v>
       </x:c>
       <x:c r="B46" s="28" t="str">
         <x:v>Bank relationship profitability scorecard</x:v>
@@ -14988,7 +14988,7 @@
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="37" t="str">
-        <x:v>TRY-00462</x:v>
+        <x:v>TRY-00480</x:v>
       </x:c>
       <x:c r="B47" s="28" t="str">
         <x:v>Bank relationship profitability scorecard</x:v>
@@ -15025,7 +15025,7 @@
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="37" t="str">
-        <x:v>TRY-00463</x:v>
+        <x:v>TRY-00481</x:v>
       </x:c>
       <x:c r="B48" s="28" t="str">
         <x:v>Bank relationship profitability scorecard</x:v>
@@ -15062,7 +15062,7 @@
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="37" t="str">
-        <x:v>TRY-00464</x:v>
+        <x:v>TRY-00482</x:v>
       </x:c>
       <x:c r="B49" s="28" t="str">
         <x:v>Bank relationship profitability scorecard</x:v>
@@ -15099,7 +15099,7 @@
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="37" t="str">
-        <x:v>TRY-00465</x:v>
+        <x:v>TRY-00483</x:v>
       </x:c>
       <x:c r="B50" s="28" t="str">
         <x:v>Bank relationship profitability scorecard</x:v>
@@ -15136,7 +15136,7 @@
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="38" t="str">
-        <x:v>TRY-00466</x:v>
+        <x:v>TRY-00484</x:v>
       </x:c>
       <x:c r="B51" s="29" t="str">
         <x:v>Bank relationship profitability scorecard</x:v>
@@ -15279,7 +15279,7 @@
         <x:v>TRY-00395</x:v>
       </x:c>
       <x:c r="B5" s="27" t="str">
-        <x:v>Complete the eight-quarter covenant forecast</x:v>
+        <x:v>FY27 covenant outlook</x:v>
       </x:c>
       <x:c r="C5" s="27" t="str">
         <x:v>Covenant policy</x:v>
@@ -15316,7 +15316,7 @@
         <x:v>TRY-00396</x:v>
       </x:c>
       <x:c r="B6" s="28" t="str">
-        <x:v>Complete the eight-quarter covenant forecast</x:v>
+        <x:v>FY27 covenant outlook</x:v>
       </x:c>
       <x:c r="C6" s="28" t="str">
         <x:v>Covenant policy</x:v>
@@ -15353,7 +15353,7 @@
         <x:v>TRY-00397</x:v>
       </x:c>
       <x:c r="B7" s="28" t="str">
-        <x:v>Complete the eight-quarter covenant forecast</x:v>
+        <x:v>FY27 covenant outlook</x:v>
       </x:c>
       <x:c r="C7" s="28" t="str">
         <x:v>Covenant policy</x:v>
@@ -15390,32 +15390,32 @@
         <x:v>TRY-00398</x:v>
       </x:c>
       <x:c r="B8" s="28" t="str">
-        <x:v>Complete the eight-quarter covenant forecast</x:v>
+        <x:v>FY27 covenant outlook</x:v>
       </x:c>
       <x:c r="C8" s="28" t="str">
-        <x:v>Historical Covenant Inputs</x:v>
+        <x:v>Covenant Downside</x:v>
       </x:c>
       <x:c r="D8" s="28" t="str">
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="E8" s="28" t="str">
-        <x:v>2025-Q4</x:v>
+        <x:v>Forecast horizon</x:v>
       </x:c>
       <x:c r="F8" s="28" t="str">
-        <x:v>Actual</x:v>
+        <x:v>Downside</x:v>
       </x:c>
       <x:c r="G8" s="28" t="str">
-        <x:v>Quarterly covenant EBITDA</x:v>
+        <x:v>Covenant EBITDA reduction</x:v>
       </x:c>
       <x:c r="H8" s="31" t="n">
-        <x:v>2850000</x:v>
+        <x:v>0.12</x:v>
       </x:c>
       <x:c r="I8" s="28" t="str"/>
       <x:c r="J8" s="28" t="str">
-        <x:v>USD</x:v>
+        <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K8" s="28" t="str">
-        <x:v>Q2 covenant history - controller tie</x:v>
+        <x:v>July treasury downside review</x:v>
       </x:c>
       <x:c r="L8" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -15427,32 +15427,32 @@
         <x:v>TRY-00399</x:v>
       </x:c>
       <x:c r="B9" s="28" t="str">
-        <x:v>Complete the eight-quarter covenant forecast</x:v>
+        <x:v>FY27 covenant outlook</x:v>
       </x:c>
       <x:c r="C9" s="28" t="str">
-        <x:v>Historical Covenant Inputs</x:v>
+        <x:v>Covenant Downside</x:v>
       </x:c>
       <x:c r="D9" s="28" t="str">
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="E9" s="28" t="str">
-        <x:v>2025-Q4</x:v>
+        <x:v>Forecast horizon</x:v>
       </x:c>
       <x:c r="F9" s="28" t="str">
-        <x:v>Actual</x:v>
+        <x:v>Downside</x:v>
       </x:c>
       <x:c r="G9" s="28" t="str">
-        <x:v>Cash interest</x:v>
+        <x:v>Cash tax factor</x:v>
       </x:c>
       <x:c r="H9" s="31" t="n">
-        <x:v>416000</x:v>
+        <x:v>0.9</x:v>
       </x:c>
       <x:c r="I9" s="28" t="str"/>
       <x:c r="J9" s="28" t="str">
-        <x:v>USD</x:v>
+        <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K9" s="28" t="str">
-        <x:v>Q2 covenant history - controller tie</x:v>
+        <x:v>July treasury downside review</x:v>
       </x:c>
       <x:c r="L9" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -15464,32 +15464,32 @@
         <x:v>TRY-00400</x:v>
       </x:c>
       <x:c r="B10" s="28" t="str">
-        <x:v>Complete the eight-quarter covenant forecast</x:v>
+        <x:v>FY27 covenant outlook</x:v>
       </x:c>
       <x:c r="C10" s="28" t="str">
-        <x:v>Historical Covenant Inputs</x:v>
+        <x:v>Covenant Downside</x:v>
       </x:c>
       <x:c r="D10" s="28" t="str">
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="E10" s="28" t="str">
-        <x:v>2025-Q4</x:v>
+        <x:v>2026-Q3</x:v>
       </x:c>
       <x:c r="F10" s="28" t="str">
-        <x:v>Actual</x:v>
+        <x:v>Downside</x:v>
       </x:c>
       <x:c r="G10" s="28" t="str">
-        <x:v>Unfunded capital expenditures</x:v>
+        <x:v>Cash interest increment</x:v>
       </x:c>
       <x:c r="H10" s="31" t="n">
-        <x:v>600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I10" s="28" t="str"/>
       <x:c r="J10" s="28" t="str">
-        <x:v>USD thousands</x:v>
+        <x:v>USD</x:v>
       </x:c>
       <x:c r="K10" s="28" t="str">
-        <x:v>Q2 covenant history - controller tie</x:v>
+        <x:v>July treasury downside review</x:v>
       </x:c>
       <x:c r="L10" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -15501,32 +15501,32 @@
         <x:v>TRY-00401</x:v>
       </x:c>
       <x:c r="B11" s="28" t="str">
-        <x:v>Complete the eight-quarter covenant forecast</x:v>
+        <x:v>FY27 covenant outlook</x:v>
       </x:c>
       <x:c r="C11" s="28" t="str">
-        <x:v>Historical Covenant Inputs</x:v>
+        <x:v>Covenant Downside</x:v>
       </x:c>
       <x:c r="D11" s="28" t="str">
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="E11" s="28" t="str">
-        <x:v>2025-Q4</x:v>
+        <x:v>2026-Q3</x:v>
       </x:c>
       <x:c r="F11" s="28" t="str">
-        <x:v>Actual</x:v>
+        <x:v>Downside</x:v>
       </x:c>
       <x:c r="G11" s="28" t="str">
-        <x:v>Cash taxes</x:v>
+        <x:v>Unfunded capex increment</x:v>
       </x:c>
       <x:c r="H11" s="31" t="n">
-        <x:v>280000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I11" s="28" t="str"/>
       <x:c r="J11" s="28" t="str">
         <x:v>USD</x:v>
       </x:c>
       <x:c r="K11" s="28" t="str">
-        <x:v>Q2 covenant history - controller tie</x:v>
+        <x:v>July treasury downside review</x:v>
       </x:c>
       <x:c r="L11" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -15538,32 +15538,32 @@
         <x:v>TRY-00402</x:v>
       </x:c>
       <x:c r="B12" s="28" t="str">
-        <x:v>Complete the eight-quarter covenant forecast</x:v>
+        <x:v>FY27 covenant outlook</x:v>
       </x:c>
       <x:c r="C12" s="28" t="str">
-        <x:v>Historical Covenant Inputs</x:v>
+        <x:v>Covenant Downside</x:v>
       </x:c>
       <x:c r="D12" s="28" t="str">
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="E12" s="28" t="str">
-        <x:v>2025-Q4</x:v>
+        <x:v>2026-Q4</x:v>
       </x:c>
       <x:c r="F12" s="28" t="str">
-        <x:v>Actual</x:v>
+        <x:v>Downside</x:v>
       </x:c>
       <x:c r="G12" s="28" t="str">
-        <x:v>Scheduled debt repayment</x:v>
+        <x:v>Cash interest increment</x:v>
       </x:c>
       <x:c r="H12" s="31" t="n">
-        <x:v>650000</x:v>
+        <x:v>75000</x:v>
       </x:c>
       <x:c r="I12" s="28" t="str"/>
       <x:c r="J12" s="28" t="str">
         <x:v>USD</x:v>
       </x:c>
       <x:c r="K12" s="28" t="str">
-        <x:v>Q2 covenant history - controller tie</x:v>
+        <x:v>July treasury downside review</x:v>
       </x:c>
       <x:c r="L12" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -15575,32 +15575,32 @@
         <x:v>TRY-00403</x:v>
       </x:c>
       <x:c r="B13" s="28" t="str">
-        <x:v>Complete the eight-quarter covenant forecast</x:v>
+        <x:v>FY27 covenant outlook</x:v>
       </x:c>
       <x:c r="C13" s="28" t="str">
-        <x:v>Historical Covenant Inputs</x:v>
+        <x:v>Covenant Downside</x:v>
       </x:c>
       <x:c r="D13" s="28" t="str">
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="E13" s="28" t="str">
-        <x:v>2026-Q1</x:v>
+        <x:v>2026-Q4</x:v>
       </x:c>
       <x:c r="F13" s="28" t="str">
-        <x:v>Actual</x:v>
+        <x:v>Downside</x:v>
       </x:c>
       <x:c r="G13" s="28" t="str">
-        <x:v>Quarterly covenant EBITDA</x:v>
+        <x:v>Unfunded capex increment</x:v>
       </x:c>
       <x:c r="H13" s="31" t="n">
-        <x:v>2920000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I13" s="28" t="str"/>
       <x:c r="J13" s="28" t="str">
         <x:v>USD</x:v>
       </x:c>
       <x:c r="K13" s="28" t="str">
-        <x:v>Q2 covenant history - controller tie</x:v>
+        <x:v>July treasury downside review</x:v>
       </x:c>
       <x:c r="L13" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -15612,32 +15612,32 @@
         <x:v>TRY-00404</x:v>
       </x:c>
       <x:c r="B14" s="28" t="str">
-        <x:v>Complete the eight-quarter covenant forecast</x:v>
+        <x:v>FY27 covenant outlook</x:v>
       </x:c>
       <x:c r="C14" s="28" t="str">
-        <x:v>Historical Covenant Inputs</x:v>
+        <x:v>Covenant Downside</x:v>
       </x:c>
       <x:c r="D14" s="28" t="str">
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="E14" s="28" t="str">
-        <x:v>2026-Q1</x:v>
+        <x:v>2027-Q1</x:v>
       </x:c>
       <x:c r="F14" s="28" t="str">
-        <x:v>Actual</x:v>
+        <x:v>Downside</x:v>
       </x:c>
       <x:c r="G14" s="28" t="str">
-        <x:v>Cash interest</x:v>
+        <x:v>Cash interest increment</x:v>
       </x:c>
       <x:c r="H14" s="31" t="n">
-        <x:v>434</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="I14" s="28" t="str"/>
       <x:c r="J14" s="28" t="str">
         <x:v>USD thousands</x:v>
       </x:c>
       <x:c r="K14" s="28" t="str">
-        <x:v>Q2 covenant history - controller tie</x:v>
+        <x:v>July treasury downside review</x:v>
       </x:c>
       <x:c r="L14" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -15649,32 +15649,32 @@
         <x:v>TRY-00405</x:v>
       </x:c>
       <x:c r="B15" s="28" t="str">
-        <x:v>Complete the eight-quarter covenant forecast</x:v>
+        <x:v>FY27 covenant outlook</x:v>
       </x:c>
       <x:c r="C15" s="28" t="str">
-        <x:v>Historical Covenant Inputs</x:v>
+        <x:v>Covenant Downside</x:v>
       </x:c>
       <x:c r="D15" s="28" t="str">
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="E15" s="28" t="str">
-        <x:v>2026-Q1</x:v>
+        <x:v>2027-Q1</x:v>
       </x:c>
       <x:c r="F15" s="28" t="str">
-        <x:v>Actual</x:v>
+        <x:v>Downside</x:v>
       </x:c>
       <x:c r="G15" s="28" t="str">
-        <x:v>Unfunded capital expenditures</x:v>
+        <x:v>Unfunded capex increment</x:v>
       </x:c>
       <x:c r="H15" s="31" t="n">
-        <x:v>610000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I15" s="28" t="str"/>
       <x:c r="J15" s="28" t="str">
         <x:v>USD</x:v>
       </x:c>
       <x:c r="K15" s="28" t="str">
-        <x:v>Q2 covenant history - controller tie</x:v>
+        <x:v>July treasury downside review</x:v>
       </x:c>
       <x:c r="L15" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -15686,32 +15686,32 @@
         <x:v>TRY-00406</x:v>
       </x:c>
       <x:c r="B16" s="28" t="str">
-        <x:v>Complete the eight-quarter covenant forecast</x:v>
+        <x:v>FY27 covenant outlook</x:v>
       </x:c>
       <x:c r="C16" s="28" t="str">
-        <x:v>Historical Covenant Inputs</x:v>
+        <x:v>Covenant Downside</x:v>
       </x:c>
       <x:c r="D16" s="28" t="str">
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="E16" s="28" t="str">
-        <x:v>2026-Q1</x:v>
+        <x:v>2027-Q2</x:v>
       </x:c>
       <x:c r="F16" s="28" t="str">
-        <x:v>Actual</x:v>
+        <x:v>Downside</x:v>
       </x:c>
       <x:c r="G16" s="28" t="str">
-        <x:v>Cash taxes</x:v>
+        <x:v>Cash interest increment</x:v>
       </x:c>
       <x:c r="H16" s="31" t="n">
-        <x:v>290000</x:v>
+        <x:v>75000</x:v>
       </x:c>
       <x:c r="I16" s="28" t="str"/>
       <x:c r="J16" s="28" t="str">
         <x:v>USD</x:v>
       </x:c>
       <x:c r="K16" s="28" t="str">
-        <x:v>Q2 covenant history - controller tie</x:v>
+        <x:v>July treasury downside review</x:v>
       </x:c>
       <x:c r="L16" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -15723,32 +15723,32 @@
         <x:v>TRY-00407</x:v>
       </x:c>
       <x:c r="B17" s="28" t="str">
-        <x:v>Complete the eight-quarter covenant forecast</x:v>
+        <x:v>FY27 covenant outlook</x:v>
       </x:c>
       <x:c r="C17" s="28" t="str">
-        <x:v>Historical Covenant Inputs</x:v>
+        <x:v>Covenant Downside</x:v>
       </x:c>
       <x:c r="D17" s="28" t="str">
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="E17" s="28" t="str">
-        <x:v>2026-Q1</x:v>
+        <x:v>2027-Q2</x:v>
       </x:c>
       <x:c r="F17" s="28" t="str">
-        <x:v>Actual</x:v>
+        <x:v>Downside</x:v>
       </x:c>
       <x:c r="G17" s="28" t="str">
-        <x:v>Scheduled debt repayment</x:v>
+        <x:v>Unfunded capex increment</x:v>
       </x:c>
       <x:c r="H17" s="31" t="n">
-        <x:v>650000</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="I17" s="28" t="str"/>
       <x:c r="J17" s="28" t="str">
         <x:v>USD</x:v>
       </x:c>
       <x:c r="K17" s="28" t="str">
-        <x:v>Q2 covenant history - controller tie</x:v>
+        <x:v>July treasury downside review</x:v>
       </x:c>
       <x:c r="L17" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -15760,32 +15760,32 @@
         <x:v>TRY-00408</x:v>
       </x:c>
       <x:c r="B18" s="28" t="str">
-        <x:v>Complete the eight-quarter covenant forecast</x:v>
+        <x:v>FY27 covenant outlook</x:v>
       </x:c>
       <x:c r="C18" s="28" t="str">
-        <x:v>Historical Covenant Inputs</x:v>
+        <x:v>Covenant Downside</x:v>
       </x:c>
       <x:c r="D18" s="28" t="str">
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="E18" s="28" t="str">
-        <x:v>2026-Q2</x:v>
+        <x:v>2027-Q3</x:v>
       </x:c>
       <x:c r="F18" s="28" t="str">
-        <x:v>Actual</x:v>
+        <x:v>Downside</x:v>
       </x:c>
       <x:c r="G18" s="28" t="str">
-        <x:v>Quarterly covenant EBITDA</x:v>
+        <x:v>Cash interest increment</x:v>
       </x:c>
       <x:c r="H18" s="31" t="n">
-        <x:v>3010</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="I18" s="28" t="str"/>
       <x:c r="J18" s="28" t="str">
         <x:v>USD thousands</x:v>
       </x:c>
       <x:c r="K18" s="28" t="str">
-        <x:v>Q2 covenant history - controller tie</x:v>
+        <x:v>July treasury downside review</x:v>
       </x:c>
       <x:c r="L18" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -15797,32 +15797,32 @@
         <x:v>TRY-00409</x:v>
       </x:c>
       <x:c r="B19" s="28" t="str">
-        <x:v>Complete the eight-quarter covenant forecast</x:v>
+        <x:v>FY27 covenant outlook</x:v>
       </x:c>
       <x:c r="C19" s="28" t="str">
-        <x:v>Historical Covenant Inputs</x:v>
+        <x:v>Covenant Downside</x:v>
       </x:c>
       <x:c r="D19" s="28" t="str">
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="E19" s="28" t="str">
-        <x:v>2026-Q2</x:v>
+        <x:v>2027-Q3</x:v>
       </x:c>
       <x:c r="F19" s="28" t="str">
-        <x:v>Actual</x:v>
+        <x:v>Downside</x:v>
       </x:c>
       <x:c r="G19" s="28" t="str">
-        <x:v>Cash interest</x:v>
+        <x:v>Unfunded capex increment</x:v>
       </x:c>
       <x:c r="H19" s="31" t="n">
-        <x:v>452000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I19" s="28" t="str"/>
       <x:c r="J19" s="28" t="str">
         <x:v>USD</x:v>
       </x:c>
       <x:c r="K19" s="28" t="str">
-        <x:v>Q2 covenant history - controller tie</x:v>
+        <x:v>July treasury downside review</x:v>
       </x:c>
       <x:c r="L19" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -15834,32 +15834,32 @@
         <x:v>TRY-00410</x:v>
       </x:c>
       <x:c r="B20" s="28" t="str">
-        <x:v>Complete the eight-quarter covenant forecast</x:v>
+        <x:v>FY27 covenant outlook</x:v>
       </x:c>
       <x:c r="C20" s="28" t="str">
-        <x:v>Historical Covenant Inputs</x:v>
+        <x:v>Covenant Downside</x:v>
       </x:c>
       <x:c r="D20" s="28" t="str">
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="E20" s="28" t="str">
-        <x:v>2026-Q2</x:v>
+        <x:v>2027-Q4</x:v>
       </x:c>
       <x:c r="F20" s="28" t="str">
-        <x:v>Actual</x:v>
+        <x:v>Downside</x:v>
       </x:c>
       <x:c r="G20" s="28" t="str">
-        <x:v>Unfunded capital expenditures</x:v>
+        <x:v>Cash interest increment</x:v>
       </x:c>
       <x:c r="H20" s="31" t="n">
-        <x:v>620000</x:v>
+        <x:v>75000</x:v>
       </x:c>
       <x:c r="I20" s="28" t="str"/>
       <x:c r="J20" s="28" t="str">
         <x:v>USD</x:v>
       </x:c>
       <x:c r="K20" s="28" t="str">
-        <x:v>Q2 covenant history - controller tie</x:v>
+        <x:v>July treasury downside review</x:v>
       </x:c>
       <x:c r="L20" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -15871,32 +15871,32 @@
         <x:v>TRY-00411</x:v>
       </x:c>
       <x:c r="B21" s="28" t="str">
-        <x:v>Complete the eight-quarter covenant forecast</x:v>
+        <x:v>FY27 covenant outlook</x:v>
       </x:c>
       <x:c r="C21" s="28" t="str">
-        <x:v>Historical Covenant Inputs</x:v>
+        <x:v>Covenant Downside</x:v>
       </x:c>
       <x:c r="D21" s="28" t="str">
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="E21" s="28" t="str">
-        <x:v>2026-Q2</x:v>
+        <x:v>2027-Q4</x:v>
       </x:c>
       <x:c r="F21" s="28" t="str">
-        <x:v>Actual</x:v>
+        <x:v>Downside</x:v>
       </x:c>
       <x:c r="G21" s="28" t="str">
-        <x:v>Cash taxes</x:v>
+        <x:v>Unfunded capex increment</x:v>
       </x:c>
       <x:c r="H21" s="31" t="n">
-        <x:v>300000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I21" s="28" t="str"/>
       <x:c r="J21" s="28" t="str">
         <x:v>USD</x:v>
       </x:c>
       <x:c r="K21" s="28" t="str">
-        <x:v>Q2 covenant history - controller tie</x:v>
+        <x:v>July treasury downside review</x:v>
       </x:c>
       <x:c r="L21" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -15908,32 +15908,32 @@
         <x:v>TRY-00412</x:v>
       </x:c>
       <x:c r="B22" s="28" t="str">
-        <x:v>Complete the eight-quarter covenant forecast</x:v>
+        <x:v>FY27 covenant outlook</x:v>
       </x:c>
       <x:c r="C22" s="28" t="str">
-        <x:v>Historical Covenant Inputs</x:v>
+        <x:v>Covenant Downside</x:v>
       </x:c>
       <x:c r="D22" s="28" t="str">
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="E22" s="28" t="str">
-        <x:v>2026-Q2</x:v>
+        <x:v>2028-Q1</x:v>
       </x:c>
       <x:c r="F22" s="28" t="str">
-        <x:v>Actual</x:v>
+        <x:v>Downside</x:v>
       </x:c>
       <x:c r="G22" s="28" t="str">
-        <x:v>Scheduled debt repayment</x:v>
+        <x:v>Cash interest increment</x:v>
       </x:c>
       <x:c r="H22" s="31" t="n">
-        <x:v>650</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="I22" s="28" t="str"/>
       <x:c r="J22" s="28" t="str">
         <x:v>USD thousands</x:v>
       </x:c>
       <x:c r="K22" s="28" t="str">
-        <x:v>Q2 covenant history - controller tie</x:v>
+        <x:v>July treasury downside review</x:v>
       </x:c>
       <x:c r="L22" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -15942,74 +15942,72 @@
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="37" t="str">
-        <x:v>TRY-00425</x:v>
+        <x:v>TRY-00413</x:v>
       </x:c>
       <x:c r="B23" s="28" t="str">
-        <x:v>Credit metrics and incremental debt capacity</x:v>
+        <x:v>FY27 covenant outlook</x:v>
       </x:c>
       <x:c r="C23" s="28" t="str">
-        <x:v>Credit population</x:v>
+        <x:v>Covenant Downside</x:v>
       </x:c>
       <x:c r="D23" s="28" t="str">
-        <x:v>Funded debt</x:v>
+        <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="E23" s="28" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>2028-Q1</x:v>
       </x:c>
       <x:c r="F23" s="28" t="str">
-        <x:v>Approved case</x:v>
+        <x:v>Downside</x:v>
       </x:c>
       <x:c r="G23" s="28" t="str">
-        <x:v>Posted debt</x:v>
+        <x:v>Unfunded capex increment</x:v>
       </x:c>
       <x:c r="H23" s="31" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I23" s="28" t="str"/>
       <x:c r="J23" s="28" t="str">
-        <x:v>ledger allocation factor</x:v>
+        <x:v>USD</x:v>
       </x:c>
       <x:c r="K23" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>July treasury downside review</x:v>
       </x:c>
       <x:c r="L23" s="34" t="str">
         <x:v>2026-06-30</x:v>
       </x:c>
-      <x:c r="M23" s="28" t="str">
-        <x:v>Vista ERP balance sheet as of 2026-06-30; accounts 2200, 2210, and 2300</x:v>
-      </x:c>
+      <x:c r="M23" s="28" t="str"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="37" t="str">
-        <x:v>TRY-00426</x:v>
+        <x:v>TRY-00414</x:v>
       </x:c>
       <x:c r="B24" s="28" t="str">
-        <x:v>Credit metrics and incremental debt capacity</x:v>
+        <x:v>FY27 covenant outlook</x:v>
       </x:c>
       <x:c r="C24" s="28" t="str">
-        <x:v>Credit population</x:v>
+        <x:v>Covenant Downside</x:v>
       </x:c>
       <x:c r="D24" s="28" t="str">
-        <x:v>Committed acquisition facility</x:v>
+        <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="E24" s="28" t="str">
-        <x:v>2026-07-15</x:v>
+        <x:v>2028-Q2</x:v>
       </x:c>
       <x:c r="F24" s="28" t="str">
-        <x:v>Approved case</x:v>
+        <x:v>Downside</x:v>
       </x:c>
       <x:c r="G24" s="28" t="str">
-        <x:v>Pro forma funded draw</x:v>
+        <x:v>Cash interest increment</x:v>
       </x:c>
       <x:c r="H24" s="31" t="n">
-        <x:v>24000000</x:v>
+        <x:v>75000</x:v>
       </x:c>
       <x:c r="I24" s="28" t="str"/>
       <x:c r="J24" s="28" t="str">
         <x:v>USD</x:v>
       </x:c>
       <x:c r="K24" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>July treasury downside review</x:v>
       </x:c>
       <x:c r="L24" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -16018,35 +16016,35 @@
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="37" t="str">
-        <x:v>TRY-00427</x:v>
+        <x:v>TRY-00415</x:v>
       </x:c>
       <x:c r="B25" s="28" t="str">
-        <x:v>Credit metrics and incremental debt capacity</x:v>
+        <x:v>FY27 covenant outlook</x:v>
       </x:c>
       <x:c r="C25" s="28" t="str">
-        <x:v>Credit policy</x:v>
+        <x:v>Covenant Downside</x:v>
       </x:c>
       <x:c r="D25" s="28" t="str">
-        <x:v>Alder Ridge</x:v>
+        <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="E25" s="28" t="str">
-        <x:v>LTM 2026-06-30</x:v>
+        <x:v>2028-Q2</x:v>
       </x:c>
       <x:c r="F25" s="28" t="str">
-        <x:v>Approved case</x:v>
+        <x:v>Downside</x:v>
       </x:c>
       <x:c r="G25" s="28" t="str">
-        <x:v>Covenant EBITDA</x:v>
+        <x:v>Unfunded capex increment</x:v>
       </x:c>
       <x:c r="H25" s="31" t="n">
-        <x:v>7850000</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="I25" s="28" t="str"/>
       <x:c r="J25" s="28" t="str">
         <x:v>USD</x:v>
       </x:c>
       <x:c r="K25" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>July treasury downside review</x:v>
       </x:c>
       <x:c r="L25" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -16055,35 +16053,35 @@
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="37" t="str">
-        <x:v>TRY-00428</x:v>
+        <x:v>TRY-00416</x:v>
       </x:c>
       <x:c r="B26" s="28" t="str">
-        <x:v>Credit metrics and incremental debt capacity</x:v>
+        <x:v>FY27 covenant outlook</x:v>
       </x:c>
       <x:c r="C26" s="28" t="str">
-        <x:v>Credit policy</x:v>
+        <x:v>Historical Covenant Inputs</x:v>
       </x:c>
       <x:c r="D26" s="28" t="str">
-        <x:v>Alder Ridge</x:v>
+        <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="E26" s="28" t="str">
-        <x:v>LTM 2026-06-30</x:v>
+        <x:v>2025-Q4</x:v>
       </x:c>
       <x:c r="F26" s="28" t="str">
-        <x:v>Approved case</x:v>
+        <x:v>Actual</x:v>
       </x:c>
       <x:c r="G26" s="28" t="str">
-        <x:v>Cash</x:v>
+        <x:v>Quarterly covenant EBITDA</x:v>
       </x:c>
       <x:c r="H26" s="31" t="n">
-        <x:v>3743.1197599999996</x:v>
+        <x:v>2850</x:v>
       </x:c>
       <x:c r="I26" s="28" t="str"/>
       <x:c r="J26" s="28" t="str">
         <x:v>USD thousands</x:v>
       </x:c>
       <x:c r="K26" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Q2 lender covenant workpaper, controller tie</x:v>
       </x:c>
       <x:c r="L26" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -16092,35 +16090,35 @@
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="37" t="str">
-        <x:v>TRY-00429</x:v>
+        <x:v>TRY-00417</x:v>
       </x:c>
       <x:c r="B27" s="28" t="str">
-        <x:v>Credit metrics and incremental debt capacity</x:v>
+        <x:v>FY27 covenant outlook</x:v>
       </x:c>
       <x:c r="C27" s="28" t="str">
-        <x:v>Credit policy</x:v>
+        <x:v>Historical Covenant Inputs</x:v>
       </x:c>
       <x:c r="D27" s="28" t="str">
-        <x:v>Alder Ridge</x:v>
+        <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="E27" s="28" t="str">
-        <x:v>LTM 2026-06-30</x:v>
+        <x:v>2025-Q4</x:v>
       </x:c>
       <x:c r="F27" s="28" t="str">
-        <x:v>Approved case</x:v>
+        <x:v>Actual</x:v>
       </x:c>
       <x:c r="G27" s="28" t="str">
         <x:v>Cash interest</x:v>
       </x:c>
       <x:c r="H27" s="31" t="n">
-        <x:v>1280000</x:v>
+        <x:v>416000</x:v>
       </x:c>
       <x:c r="I27" s="28" t="str"/>
       <x:c r="J27" s="28" t="str">
         <x:v>USD</x:v>
       </x:c>
       <x:c r="K27" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Q2 lender covenant workpaper, controller tie</x:v>
       </x:c>
       <x:c r="L27" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -16129,35 +16127,35 @@
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="37" t="str">
-        <x:v>TRY-00430</x:v>
+        <x:v>TRY-00418</x:v>
       </x:c>
       <x:c r="B28" s="28" t="str">
-        <x:v>Credit metrics and incremental debt capacity</x:v>
+        <x:v>FY27 covenant outlook</x:v>
       </x:c>
       <x:c r="C28" s="28" t="str">
-        <x:v>Credit policy</x:v>
+        <x:v>Historical Covenant Inputs</x:v>
       </x:c>
       <x:c r="D28" s="28" t="str">
-        <x:v>Alder Ridge</x:v>
+        <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="E28" s="28" t="str">
-        <x:v>LTM 2026-06-30</x:v>
+        <x:v>2025-Q4</x:v>
       </x:c>
       <x:c r="F28" s="28" t="str">
-        <x:v>Approved case</x:v>
+        <x:v>Actual</x:v>
       </x:c>
       <x:c r="G28" s="28" t="str">
-        <x:v>Cash taxes</x:v>
+        <x:v>Unfunded capital expenditures</x:v>
       </x:c>
       <x:c r="H28" s="31" t="n">
-        <x:v>920000</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="I28" s="28" t="str"/>
       <x:c r="J28" s="28" t="str">
         <x:v>USD</x:v>
       </x:c>
       <x:c r="K28" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Q2 lender covenant workpaper, controller tie</x:v>
       </x:c>
       <x:c r="L28" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -16166,35 +16164,35 @@
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="37" t="str">
-        <x:v>TRY-00431</x:v>
+        <x:v>TRY-00419</x:v>
       </x:c>
       <x:c r="B29" s="28" t="str">
-        <x:v>Credit metrics and incremental debt capacity</x:v>
+        <x:v>FY27 covenant outlook</x:v>
       </x:c>
       <x:c r="C29" s="28" t="str">
-        <x:v>Credit policy</x:v>
+        <x:v>Historical Covenant Inputs</x:v>
       </x:c>
       <x:c r="D29" s="28" t="str">
-        <x:v>Alder Ridge</x:v>
+        <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="E29" s="28" t="str">
-        <x:v>LTM 2026-06-30</x:v>
+        <x:v>2025-Q4</x:v>
       </x:c>
       <x:c r="F29" s="28" t="str">
-        <x:v>Approved case</x:v>
+        <x:v>Actual</x:v>
       </x:c>
       <x:c r="G29" s="28" t="str">
-        <x:v>Maintenance capex</x:v>
+        <x:v>Cash taxes</x:v>
       </x:c>
       <x:c r="H29" s="31" t="n">
-        <x:v>1350000</x:v>
+        <x:v>280000</x:v>
       </x:c>
       <x:c r="I29" s="28" t="str"/>
       <x:c r="J29" s="28" t="str">
         <x:v>USD</x:v>
       </x:c>
       <x:c r="K29" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Q2 lender covenant workpaper, controller tie</x:v>
       </x:c>
       <x:c r="L29" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -16203,35 +16201,35 @@
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="37" t="str">
-        <x:v>TRY-00432</x:v>
+        <x:v>TRY-00420</x:v>
       </x:c>
       <x:c r="B30" s="28" t="str">
-        <x:v>Credit metrics and incremental debt capacity</x:v>
+        <x:v>FY27 covenant outlook</x:v>
       </x:c>
       <x:c r="C30" s="28" t="str">
-        <x:v>Credit policy</x:v>
+        <x:v>Historical Covenant Inputs</x:v>
       </x:c>
       <x:c r="D30" s="28" t="str">
-        <x:v>Alder Ridge</x:v>
+        <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="E30" s="28" t="str">
-        <x:v>LTM 2026-06-30</x:v>
+        <x:v>2025-Q4</x:v>
       </x:c>
       <x:c r="F30" s="28" t="str">
-        <x:v>Approved case</x:v>
+        <x:v>Actual</x:v>
       </x:c>
       <x:c r="G30" s="28" t="str">
-        <x:v>Distributions</x:v>
+        <x:v>Scheduled debt repayment</x:v>
       </x:c>
       <x:c r="H30" s="31" t="n">
-        <x:v>450</x:v>
+        <x:v>650</x:v>
       </x:c>
       <x:c r="I30" s="28" t="str"/>
       <x:c r="J30" s="28" t="str">
         <x:v>USD thousands</x:v>
       </x:c>
       <x:c r="K30" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Q2 lender covenant workpaper, controller tie</x:v>
       </x:c>
       <x:c r="L30" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -16240,35 +16238,35 @@
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="37" t="str">
-        <x:v>TRY-00433</x:v>
+        <x:v>TRY-00421</x:v>
       </x:c>
       <x:c r="B31" s="28" t="str">
-        <x:v>Credit metrics and incremental debt capacity</x:v>
+        <x:v>FY27 covenant outlook</x:v>
       </x:c>
       <x:c r="C31" s="28" t="str">
-        <x:v>Credit policy</x:v>
+        <x:v>Historical Covenant Inputs</x:v>
       </x:c>
       <x:c r="D31" s="28" t="str">
-        <x:v>Alder Ridge</x:v>
+        <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="E31" s="28" t="str">
-        <x:v>LTM 2026-06-30</x:v>
+        <x:v>2026-Q1</x:v>
       </x:c>
       <x:c r="F31" s="28" t="str">
-        <x:v>Approved case</x:v>
+        <x:v>Actual</x:v>
       </x:c>
       <x:c r="G31" s="28" t="str">
-        <x:v>Tangible net worth</x:v>
+        <x:v>Quarterly covenant EBITDA</x:v>
       </x:c>
       <x:c r="H31" s="31" t="n">
-        <x:v>23100000</x:v>
+        <x:v>2920000</x:v>
       </x:c>
       <x:c r="I31" s="28" t="str"/>
       <x:c r="J31" s="28" t="str">
         <x:v>USD</x:v>
       </x:c>
       <x:c r="K31" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Q2 lender covenant workpaper, controller tie</x:v>
       </x:c>
       <x:c r="L31" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -16277,35 +16275,35 @@
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="37" t="str">
-        <x:v>TRY-00434</x:v>
+        <x:v>TRY-00422</x:v>
       </x:c>
       <x:c r="B32" s="28" t="str">
-        <x:v>Credit metrics and incremental debt capacity</x:v>
+        <x:v>FY27 covenant outlook</x:v>
       </x:c>
       <x:c r="C32" s="28" t="str">
-        <x:v>Credit policy</x:v>
+        <x:v>Historical Covenant Inputs</x:v>
       </x:c>
       <x:c r="D32" s="28" t="str">
-        <x:v>Alder Ridge</x:v>
+        <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="E32" s="28" t="str">
-        <x:v>LTM 2026-06-30</x:v>
+        <x:v>2026-Q1</x:v>
       </x:c>
       <x:c r="F32" s="28" t="str">
-        <x:v>Approved case</x:v>
+        <x:v>Actual</x:v>
       </x:c>
       <x:c r="G32" s="28" t="str">
-        <x:v>Minimum tangible net worth</x:v>
+        <x:v>Cash interest</x:v>
       </x:c>
       <x:c r="H32" s="31" t="n">
-        <x:v>18500000</x:v>
+        <x:v>434000</x:v>
       </x:c>
       <x:c r="I32" s="28" t="str"/>
       <x:c r="J32" s="28" t="str">
         <x:v>USD</x:v>
       </x:c>
       <x:c r="K32" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Q2 lender covenant workpaper, controller tie</x:v>
       </x:c>
       <x:c r="L32" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -16314,35 +16312,35 @@
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="37" t="str">
-        <x:v>TRY-00435</x:v>
+        <x:v>TRY-00423</x:v>
       </x:c>
       <x:c r="B33" s="28" t="str">
-        <x:v>Credit metrics and incremental debt capacity</x:v>
+        <x:v>FY27 covenant outlook</x:v>
       </x:c>
       <x:c r="C33" s="28" t="str">
-        <x:v>Credit policy</x:v>
+        <x:v>Historical Covenant Inputs</x:v>
       </x:c>
       <x:c r="D33" s="28" t="str">
-        <x:v>Alder Ridge</x:v>
+        <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="E33" s="28" t="str">
-        <x:v>LTM 2026-06-30</x:v>
+        <x:v>2026-Q1</x:v>
       </x:c>
       <x:c r="F33" s="28" t="str">
-        <x:v>Approved case</x:v>
+        <x:v>Actual</x:v>
       </x:c>
       <x:c r="G33" s="28" t="str">
-        <x:v>Maximum gross leverage</x:v>
+        <x:v>Unfunded capital expenditures</x:v>
       </x:c>
       <x:c r="H33" s="31" t="n">
-        <x:v>3.25</x:v>
+        <x:v>610000</x:v>
       </x:c>
       <x:c r="I33" s="28" t="str"/>
       <x:c r="J33" s="28" t="str">
-        <x:v>multiple</x:v>
+        <x:v>USD</x:v>
       </x:c>
       <x:c r="K33" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Q2 lender covenant workpaper, controller tie</x:v>
       </x:c>
       <x:c r="L33" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -16351,35 +16349,35 @@
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="37" t="str">
-        <x:v>TRY-00436</x:v>
+        <x:v>TRY-00424</x:v>
       </x:c>
       <x:c r="B34" s="28" t="str">
-        <x:v>Credit metrics and incremental debt capacity</x:v>
+        <x:v>FY27 covenant outlook</x:v>
       </x:c>
       <x:c r="C34" s="28" t="str">
-        <x:v>Credit policy</x:v>
+        <x:v>Historical Covenant Inputs</x:v>
       </x:c>
       <x:c r="D34" s="28" t="str">
-        <x:v>Alder Ridge</x:v>
+        <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="E34" s="28" t="str">
-        <x:v>LTM 2026-06-30</x:v>
+        <x:v>2026-Q1</x:v>
       </x:c>
       <x:c r="F34" s="28" t="str">
-        <x:v>Approved case</x:v>
+        <x:v>Actual</x:v>
       </x:c>
       <x:c r="G34" s="28" t="str">
-        <x:v>Minimum interest coverage</x:v>
+        <x:v>Cash taxes</x:v>
       </x:c>
       <x:c r="H34" s="31" t="n">
-        <x:v>3</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="I34" s="28" t="str"/>
       <x:c r="J34" s="28" t="str">
-        <x:v>multiple</x:v>
+        <x:v>USD thousands</x:v>
       </x:c>
       <x:c r="K34" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Q2 lender covenant workpaper, controller tie</x:v>
       </x:c>
       <x:c r="L34" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -16388,35 +16386,35 @@
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="37" t="str">
-        <x:v>TRY-00437</x:v>
+        <x:v>TRY-00425</x:v>
       </x:c>
       <x:c r="B35" s="28" t="str">
-        <x:v>Credit metrics and incremental debt capacity</x:v>
+        <x:v>FY27 covenant outlook</x:v>
       </x:c>
       <x:c r="C35" s="28" t="str">
-        <x:v>Credit policy</x:v>
+        <x:v>Historical Covenant Inputs</x:v>
       </x:c>
       <x:c r="D35" s="28" t="str">
-        <x:v>Alder Ridge</x:v>
+        <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="E35" s="28" t="str">
-        <x:v>LTM 2026-06-30</x:v>
+        <x:v>2026-Q1</x:v>
       </x:c>
       <x:c r="F35" s="28" t="str">
-        <x:v>Approved case</x:v>
+        <x:v>Actual</x:v>
       </x:c>
       <x:c r="G35" s="28" t="str">
-        <x:v>Minimum fixed-charge coverage</x:v>
+        <x:v>Scheduled debt repayment</x:v>
       </x:c>
       <x:c r="H35" s="31" t="n">
-        <x:v>1.35</x:v>
+        <x:v>650000</x:v>
       </x:c>
       <x:c r="I35" s="28" t="str"/>
       <x:c r="J35" s="28" t="str">
-        <x:v>multiple</x:v>
+        <x:v>USD</x:v>
       </x:c>
       <x:c r="K35" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Q2 lender covenant workpaper, controller tie</x:v>
       </x:c>
       <x:c r="L35" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -16425,35 +16423,35 @@
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="37" t="str">
-        <x:v>TRY-00438</x:v>
+        <x:v>TRY-00426</x:v>
       </x:c>
       <x:c r="B36" s="28" t="str">
-        <x:v>Credit metrics and incremental debt capacity</x:v>
+        <x:v>FY27 covenant outlook</x:v>
       </x:c>
       <x:c r="C36" s="28" t="str">
-        <x:v>Credit policy</x:v>
+        <x:v>Historical Covenant Inputs</x:v>
       </x:c>
       <x:c r="D36" s="28" t="str">
-        <x:v>Alder Ridge</x:v>
+        <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="E36" s="28" t="str">
-        <x:v>LTM 2026-06-30</x:v>
+        <x:v>2026-Q2</x:v>
       </x:c>
       <x:c r="F36" s="28" t="str">
-        <x:v>Approved case</x:v>
+        <x:v>Actual</x:v>
       </x:c>
       <x:c r="G36" s="28" t="str">
-        <x:v>Internal ratings debt cap</x:v>
+        <x:v>Quarterly covenant EBITDA</x:v>
       </x:c>
       <x:c r="H36" s="31" t="n">
-        <x:v>12000000</x:v>
+        <x:v>3010000</x:v>
       </x:c>
       <x:c r="I36" s="28" t="str"/>
       <x:c r="J36" s="28" t="str">
         <x:v>USD</x:v>
       </x:c>
       <x:c r="K36" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Q2 lender covenant workpaper, controller tie</x:v>
       </x:c>
       <x:c r="L36" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -16462,35 +16460,35 @@
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="37" t="str">
-        <x:v>TRY-00439</x:v>
+        <x:v>TRY-00427</x:v>
       </x:c>
       <x:c r="B37" s="28" t="str">
-        <x:v>Credit metrics and incremental debt capacity</x:v>
+        <x:v>FY27 covenant outlook</x:v>
       </x:c>
       <x:c r="C37" s="28" t="str">
-        <x:v>Credit policy</x:v>
+        <x:v>Historical Covenant Inputs</x:v>
       </x:c>
       <x:c r="D37" s="28" t="str">
-        <x:v>Alder Ridge</x:v>
+        <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="E37" s="28" t="str">
-        <x:v>LTM 2026-06-30</x:v>
+        <x:v>2026-Q2</x:v>
       </x:c>
       <x:c r="F37" s="28" t="str">
-        <x:v>Approved case</x:v>
+        <x:v>Actual</x:v>
       </x:c>
       <x:c r="G37" s="28" t="str">
-        <x:v>Incremental debt interest rate</x:v>
+        <x:v>Cash interest</x:v>
       </x:c>
       <x:c r="H37" s="31" t="n">
-        <x:v>0.075</x:v>
+        <x:v>452000</x:v>
       </x:c>
       <x:c r="I37" s="28" t="str"/>
       <x:c r="J37" s="28" t="str">
-        <x:v>decimal ratio</x:v>
+        <x:v>USD</x:v>
       </x:c>
       <x:c r="K37" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Q2 lender covenant workpaper, controller tie</x:v>
       </x:c>
       <x:c r="L37" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -16499,35 +16497,35 @@
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="37" t="str">
-        <x:v>TRY-00720</x:v>
+        <x:v>TRY-00428</x:v>
       </x:c>
       <x:c r="B38" s="28" t="str">
-        <x:v>ABL borrowing base and covenant cure</x:v>
+        <x:v>FY27 covenant outlook</x:v>
       </x:c>
       <x:c r="C38" s="28" t="str">
-        <x:v>ABL borrowing base</x:v>
+        <x:v>Historical Covenant Inputs</x:v>
       </x:c>
       <x:c r="D38" s="28" t="str">
-        <x:v>Eligible accounts receivable</x:v>
+        <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="E38" s="28" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>2026-Q2</x:v>
       </x:c>
       <x:c r="F38" s="28" t="str">
-        <x:v>Approved case</x:v>
+        <x:v>Actual</x:v>
       </x:c>
       <x:c r="G38" s="28" t="str">
-        <x:v>Gross eligible collateral</x:v>
+        <x:v>Unfunded capital expenditures</x:v>
       </x:c>
       <x:c r="H38" s="31" t="n">
-        <x:v>11850000</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="I38" s="28" t="str"/>
       <x:c r="J38" s="28" t="str">
-        <x:v>USD</x:v>
+        <x:v>USD thousands</x:v>
       </x:c>
       <x:c r="K38" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Q2 lender covenant workpaper, controller tie</x:v>
       </x:c>
       <x:c r="L38" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -16536,35 +16534,35 @@
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="37" t="str">
-        <x:v>TRY-00721</x:v>
+        <x:v>TRY-00429</x:v>
       </x:c>
       <x:c r="B39" s="28" t="str">
-        <x:v>ABL borrowing base and covenant cure</x:v>
+        <x:v>FY27 covenant outlook</x:v>
       </x:c>
       <x:c r="C39" s="28" t="str">
-        <x:v>ABL borrowing base</x:v>
+        <x:v>Historical Covenant Inputs</x:v>
       </x:c>
       <x:c r="D39" s="28" t="str">
-        <x:v>Eligible accounts receivable</x:v>
+        <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="E39" s="28" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>2026-Q2</x:v>
       </x:c>
       <x:c r="F39" s="28" t="str">
-        <x:v>Approved case</x:v>
+        <x:v>Actual</x:v>
       </x:c>
       <x:c r="G39" s="28" t="str">
-        <x:v>Advance rate</x:v>
+        <x:v>Cash taxes</x:v>
       </x:c>
       <x:c r="H39" s="31" t="n">
-        <x:v>0.85</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I39" s="28" t="str"/>
       <x:c r="J39" s="28" t="str">
-        <x:v>decimal ratio</x:v>
+        <x:v>USD</x:v>
       </x:c>
       <x:c r="K39" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Q2 lender covenant workpaper, controller tie</x:v>
       </x:c>
       <x:c r="L39" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -16573,35 +16571,35 @@
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="37" t="str">
-        <x:v>TRY-00722</x:v>
+        <x:v>TRY-00430</x:v>
       </x:c>
       <x:c r="B40" s="28" t="str">
-        <x:v>ABL borrowing base and covenant cure</x:v>
+        <x:v>FY27 covenant outlook</x:v>
       </x:c>
       <x:c r="C40" s="28" t="str">
-        <x:v>ABL borrowing base</x:v>
+        <x:v>Historical Covenant Inputs</x:v>
       </x:c>
       <x:c r="D40" s="28" t="str">
-        <x:v>Eligible accounts receivable</x:v>
+        <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="E40" s="28" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>2026-Q2</x:v>
       </x:c>
       <x:c r="F40" s="28" t="str">
-        <x:v>Approved case</x:v>
+        <x:v>Actual</x:v>
       </x:c>
       <x:c r="G40" s="28" t="str">
-        <x:v>Specific reserve</x:v>
+        <x:v>Scheduled debt repayment</x:v>
       </x:c>
       <x:c r="H40" s="31" t="n">
-        <x:v>1420000</x:v>
+        <x:v>650000</x:v>
       </x:c>
       <x:c r="I40" s="28" t="str"/>
       <x:c r="J40" s="28" t="str">
         <x:v>USD</x:v>
       </x:c>
       <x:c r="K40" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Q2 lender covenant workpaper, controller tie</x:v>
       </x:c>
       <x:c r="L40" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -16610,16 +16608,16 @@
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="37" t="str">
-        <x:v>TRY-00723</x:v>
+        <x:v>TRY-00443</x:v>
       </x:c>
       <x:c r="B41" s="28" t="str">
-        <x:v>ABL borrowing base and covenant cure</x:v>
+        <x:v>Credit metrics and incremental debt capacity</x:v>
       </x:c>
       <x:c r="C41" s="28" t="str">
-        <x:v>ABL borrowing base</x:v>
+        <x:v>Credit population</x:v>
       </x:c>
       <x:c r="D41" s="28" t="str">
-        <x:v>Eligible inventory</x:v>
+        <x:v>Funded debt</x:v>
       </x:c>
       <x:c r="E41" s="28" t="str">
         <x:v>2026-06-30</x:v>
@@ -16628,14 +16626,14 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G41" s="28" t="str">
-        <x:v>Gross eligible collateral</x:v>
+        <x:v>Posted debt</x:v>
       </x:c>
       <x:c r="H41" s="31" t="n">
-        <x:v>3600</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I41" s="28" t="str"/>
       <x:c r="J41" s="28" t="str">
-        <x:v>USD thousands</x:v>
+        <x:v>ledger allocation factor</x:v>
       </x:c>
       <x:c r="K41" s="28" t="str">
         <x:v>Finance operating schedule</x:v>
@@ -16643,36 +16641,38 @@
       <x:c r="L41" s="34" t="str">
         <x:v>2026-06-30</x:v>
       </x:c>
-      <x:c r="M41" s="28" t="str"/>
+      <x:c r="M41" s="28" t="str">
+        <x:v>Vista ERP balance sheet as of 2026-06-30; accounts 2200, 2210, and 2300</x:v>
+      </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="37" t="str">
-        <x:v>TRY-00724</x:v>
+        <x:v>TRY-00444</x:v>
       </x:c>
       <x:c r="B42" s="28" t="str">
-        <x:v>ABL borrowing base and covenant cure</x:v>
+        <x:v>Credit metrics and incremental debt capacity</x:v>
       </x:c>
       <x:c r="C42" s="28" t="str">
-        <x:v>ABL borrowing base</x:v>
+        <x:v>Credit population</x:v>
       </x:c>
       <x:c r="D42" s="28" t="str">
-        <x:v>Eligible inventory</x:v>
+        <x:v>Committed acquisition facility</x:v>
       </x:c>
       <x:c r="E42" s="28" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>2026-07-15</x:v>
       </x:c>
       <x:c r="F42" s="28" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G42" s="28" t="str">
-        <x:v>Advance rate</x:v>
+        <x:v>Pro forma funded draw</x:v>
       </x:c>
       <x:c r="H42" s="31" t="n">
-        <x:v>0.5</x:v>
+        <x:v>24000000</x:v>
       </x:c>
       <x:c r="I42" s="28" t="str"/>
       <x:c r="J42" s="28" t="str">
-        <x:v>decimal ratio</x:v>
+        <x:v>USD</x:v>
       </x:c>
       <x:c r="K42" s="28" t="str">
         <x:v>Finance operating schedule</x:v>
@@ -16684,28 +16684,28 @@
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="37" t="str">
-        <x:v>TRY-00725</x:v>
+        <x:v>TRY-00445</x:v>
       </x:c>
       <x:c r="B43" s="28" t="str">
-        <x:v>ABL borrowing base and covenant cure</x:v>
+        <x:v>Credit metrics and incremental debt capacity</x:v>
       </x:c>
       <x:c r="C43" s="28" t="str">
-        <x:v>ABL borrowing base</x:v>
+        <x:v>Credit policy</x:v>
       </x:c>
       <x:c r="D43" s="28" t="str">
-        <x:v>Eligible inventory</x:v>
+        <x:v>Alder Ridge</x:v>
       </x:c>
       <x:c r="E43" s="28" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>LTM 2026-06-30</x:v>
       </x:c>
       <x:c r="F43" s="28" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G43" s="28" t="str">
-        <x:v>Specific reserve</x:v>
+        <x:v>Covenant EBITDA</x:v>
       </x:c>
       <x:c r="H43" s="31" t="n">
-        <x:v>440000</x:v>
+        <x:v>7850000</x:v>
       </x:c>
       <x:c r="I43" s="28" t="str"/>
       <x:c r="J43" s="28" t="str">
@@ -16721,32 +16721,32 @@
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="37" t="str">
-        <x:v>TRY-00726</x:v>
+        <x:v>TRY-00446</x:v>
       </x:c>
       <x:c r="B44" s="28" t="str">
-        <x:v>ABL borrowing base and covenant cure</x:v>
+        <x:v>Credit metrics and incremental debt capacity</x:v>
       </x:c>
       <x:c r="C44" s="28" t="str">
-        <x:v>ABL borrowing base</x:v>
+        <x:v>Credit policy</x:v>
       </x:c>
       <x:c r="D44" s="28" t="str">
-        <x:v>Eligible equipment</x:v>
+        <x:v>Alder Ridge</x:v>
       </x:c>
       <x:c r="E44" s="28" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>LTM 2026-06-30</x:v>
       </x:c>
       <x:c r="F44" s="28" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G44" s="28" t="str">
-        <x:v>Gross eligible collateral</x:v>
+        <x:v>Cash</x:v>
       </x:c>
       <x:c r="H44" s="31" t="n">
-        <x:v>5200000</x:v>
+        <x:v>3743.1197599999996</x:v>
       </x:c>
       <x:c r="I44" s="28" t="str"/>
       <x:c r="J44" s="28" t="str">
-        <x:v>USD</x:v>
+        <x:v>USD thousands</x:v>
       </x:c>
       <x:c r="K44" s="28" t="str">
         <x:v>Finance operating schedule</x:v>
@@ -16758,32 +16758,32 @@
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="37" t="str">
-        <x:v>TRY-00727</x:v>
+        <x:v>TRY-00447</x:v>
       </x:c>
       <x:c r="B45" s="28" t="str">
-        <x:v>ABL borrowing base and covenant cure</x:v>
+        <x:v>Credit metrics and incremental debt capacity</x:v>
       </x:c>
       <x:c r="C45" s="28" t="str">
-        <x:v>ABL borrowing base</x:v>
+        <x:v>Credit policy</x:v>
       </x:c>
       <x:c r="D45" s="28" t="str">
-        <x:v>Eligible equipment</x:v>
+        <x:v>Alder Ridge</x:v>
       </x:c>
       <x:c r="E45" s="28" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>LTM 2026-06-30</x:v>
       </x:c>
       <x:c r="F45" s="28" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G45" s="28" t="str">
-        <x:v>Advance rate</x:v>
+        <x:v>Cash interest</x:v>
       </x:c>
       <x:c r="H45" s="31" t="n">
-        <x:v>0.35</x:v>
+        <x:v>1280000</x:v>
       </x:c>
       <x:c r="I45" s="28" t="str"/>
       <x:c r="J45" s="28" t="str">
-        <x:v>decimal ratio</x:v>
+        <x:v>USD</x:v>
       </x:c>
       <x:c r="K45" s="28" t="str">
         <x:v>Finance operating schedule</x:v>
@@ -16795,28 +16795,28 @@
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="37" t="str">
-        <x:v>TRY-00728</x:v>
+        <x:v>TRY-00448</x:v>
       </x:c>
       <x:c r="B46" s="28" t="str">
-        <x:v>ABL borrowing base and covenant cure</x:v>
+        <x:v>Credit metrics and incremental debt capacity</x:v>
       </x:c>
       <x:c r="C46" s="28" t="str">
-        <x:v>ABL borrowing base</x:v>
+        <x:v>Credit policy</x:v>
       </x:c>
       <x:c r="D46" s="28" t="str">
-        <x:v>Eligible equipment</x:v>
+        <x:v>Alder Ridge</x:v>
       </x:c>
       <x:c r="E46" s="28" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>LTM 2026-06-30</x:v>
       </x:c>
       <x:c r="F46" s="28" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G46" s="28" t="str">
-        <x:v>Specific reserve</x:v>
+        <x:v>Cash taxes</x:v>
       </x:c>
       <x:c r="H46" s="31" t="n">
-        <x:v>0</x:v>
+        <x:v>920000</x:v>
       </x:c>
       <x:c r="I46" s="28" t="str"/>
       <x:c r="J46" s="28" t="str">
@@ -16832,28 +16832,28 @@
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="37" t="str">
-        <x:v>TRY-00729</x:v>
+        <x:v>TRY-00449</x:v>
       </x:c>
       <x:c r="B47" s="28" t="str">
-        <x:v>ABL borrowing base and covenant cure</x:v>
+        <x:v>Credit metrics and incremental debt capacity</x:v>
       </x:c>
       <x:c r="C47" s="28" t="str">
-        <x:v>ABL eligibility exclusions</x:v>
+        <x:v>Credit policy</x:v>
       </x:c>
       <x:c r="D47" s="28" t="str">
-        <x:v>AR over 90 days</x:v>
+        <x:v>Alder Ridge</x:v>
       </x:c>
       <x:c r="E47" s="28" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>LTM 2026-06-30</x:v>
       </x:c>
       <x:c r="F47" s="28" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G47" s="28" t="str">
-        <x:v>Excluded amount</x:v>
+        <x:v>Maintenance capex</x:v>
       </x:c>
       <x:c r="H47" s="31" t="n">
-        <x:v>760000</x:v>
+        <x:v>1350000</x:v>
       </x:c>
       <x:c r="I47" s="28" t="str"/>
       <x:c r="J47" s="28" t="str">
@@ -16869,32 +16869,32 @@
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="37" t="str">
-        <x:v>TRY-00730</x:v>
+        <x:v>TRY-00450</x:v>
       </x:c>
       <x:c r="B48" s="28" t="str">
-        <x:v>ABL borrowing base and covenant cure</x:v>
+        <x:v>Credit metrics and incremental debt capacity</x:v>
       </x:c>
       <x:c r="C48" s="28" t="str">
-        <x:v>ABL eligibility exclusions</x:v>
+        <x:v>Credit policy</x:v>
       </x:c>
       <x:c r="D48" s="28" t="str">
-        <x:v>Cross-aged customers</x:v>
+        <x:v>Alder Ridge</x:v>
       </x:c>
       <x:c r="E48" s="28" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>LTM 2026-06-30</x:v>
       </x:c>
       <x:c r="F48" s="28" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G48" s="28" t="str">
-        <x:v>Excluded amount</x:v>
+        <x:v>Distributions</x:v>
       </x:c>
       <x:c r="H48" s="31" t="n">
-        <x:v>540000</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="I48" s="28" t="str"/>
       <x:c r="J48" s="28" t="str">
-        <x:v>USD</x:v>
+        <x:v>USD thousands</x:v>
       </x:c>
       <x:c r="K48" s="28" t="str">
         <x:v>Finance operating schedule</x:v>
@@ -16906,32 +16906,32 @@
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="37" t="str">
-        <x:v>TRY-00731</x:v>
+        <x:v>TRY-00451</x:v>
       </x:c>
       <x:c r="B49" s="28" t="str">
-        <x:v>ABL borrowing base and covenant cure</x:v>
+        <x:v>Credit metrics and incremental debt capacity</x:v>
       </x:c>
       <x:c r="C49" s="28" t="str">
-        <x:v>ABL eligibility exclusions</x:v>
+        <x:v>Credit policy</x:v>
       </x:c>
       <x:c r="D49" s="28" t="str">
-        <x:v>Related-party AR</x:v>
+        <x:v>Alder Ridge</x:v>
       </x:c>
       <x:c r="E49" s="28" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>LTM 2026-06-30</x:v>
       </x:c>
       <x:c r="F49" s="28" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G49" s="28" t="str">
-        <x:v>Excluded amount</x:v>
+        <x:v>Tangible net worth</x:v>
       </x:c>
       <x:c r="H49" s="31" t="n">
-        <x:v>180</x:v>
+        <x:v>23100000</x:v>
       </x:c>
       <x:c r="I49" s="28" t="str"/>
       <x:c r="J49" s="28" t="str">
-        <x:v>USD thousands</x:v>
+        <x:v>USD</x:v>
       </x:c>
       <x:c r="K49" s="28" t="str">
         <x:v>Finance operating schedule</x:v>
@@ -16943,28 +16943,28 @@
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="37" t="str">
-        <x:v>TRY-00732</x:v>
+        <x:v>TRY-00452</x:v>
       </x:c>
       <x:c r="B50" s="28" t="str">
-        <x:v>ABL borrowing base and covenant cure</x:v>
+        <x:v>Credit metrics and incremental debt capacity</x:v>
       </x:c>
       <x:c r="C50" s="28" t="str">
-        <x:v>ABL eligibility exclusions</x:v>
+        <x:v>Credit policy</x:v>
       </x:c>
       <x:c r="D50" s="28" t="str">
-        <x:v>Obsolete inventory</x:v>
+        <x:v>Alder Ridge</x:v>
       </x:c>
       <x:c r="E50" s="28" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>LTM 2026-06-30</x:v>
       </x:c>
       <x:c r="F50" s="28" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G50" s="28" t="str">
-        <x:v>Excluded amount</x:v>
+        <x:v>Minimum tangible net worth</x:v>
       </x:c>
       <x:c r="H50" s="31" t="n">
-        <x:v>390000</x:v>
+        <x:v>18500000</x:v>
       </x:c>
       <x:c r="I50" s="28" t="str"/>
       <x:c r="J50" s="28" t="str">
@@ -16980,32 +16980,32 @@
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="37" t="str">
-        <x:v>TRY-00733</x:v>
+        <x:v>TRY-00453</x:v>
       </x:c>
       <x:c r="B51" s="28" t="str">
-        <x:v>ABL borrowing base and covenant cure</x:v>
+        <x:v>Credit metrics and incremental debt capacity</x:v>
       </x:c>
       <x:c r="C51" s="28" t="str">
-        <x:v>ABL covenant inputs</x:v>
+        <x:v>Credit policy</x:v>
       </x:c>
       <x:c r="D51" s="28" t="str">
         <x:v>Alder Ridge</x:v>
       </x:c>
       <x:c r="E51" s="28" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>LTM 2026-06-30</x:v>
       </x:c>
       <x:c r="F51" s="28" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G51" s="28" t="str">
-        <x:v>Facility commitment</x:v>
+        <x:v>Maximum gross leverage</x:v>
       </x:c>
       <x:c r="H51" s="31" t="n">
-        <x:v>12000000</x:v>
+        <x:v>3.25</x:v>
       </x:c>
       <x:c r="I51" s="28" t="str"/>
       <x:c r="J51" s="28" t="str">
-        <x:v>USD</x:v>
+        <x:v>multiple</x:v>
       </x:c>
       <x:c r="K51" s="28" t="str">
         <x:v>Finance operating schedule</x:v>
@@ -17017,32 +17017,32 @@
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="37" t="str">
-        <x:v>TRY-00734</x:v>
+        <x:v>TRY-00454</x:v>
       </x:c>
       <x:c r="B52" s="28" t="str">
-        <x:v>ABL borrowing base and covenant cure</x:v>
+        <x:v>Credit metrics and incremental debt capacity</x:v>
       </x:c>
       <x:c r="C52" s="28" t="str">
-        <x:v>ABL covenant inputs</x:v>
+        <x:v>Credit policy</x:v>
       </x:c>
       <x:c r="D52" s="28" t="str">
         <x:v>Alder Ridge</x:v>
       </x:c>
       <x:c r="E52" s="28" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>LTM 2026-06-30</x:v>
       </x:c>
       <x:c r="F52" s="28" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G52" s="28" t="str">
-        <x:v>Existing letters of credit</x:v>
+        <x:v>Minimum interest coverage</x:v>
       </x:c>
       <x:c r="H52" s="31" t="n">
-        <x:v>850000</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="I52" s="28" t="str"/>
       <x:c r="J52" s="28" t="str">
-        <x:v>USD</x:v>
+        <x:v>multiple</x:v>
       </x:c>
       <x:c r="K52" s="28" t="str">
         <x:v>Finance operating schedule</x:v>
@@ -17054,32 +17054,32 @@
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="37" t="str">
-        <x:v>TRY-00735</x:v>
+        <x:v>TRY-00455</x:v>
       </x:c>
       <x:c r="B53" s="28" t="str">
-        <x:v>ABL borrowing base and covenant cure</x:v>
+        <x:v>Credit metrics and incremental debt capacity</x:v>
       </x:c>
       <x:c r="C53" s="28" t="str">
-        <x:v>ABL covenant inputs</x:v>
+        <x:v>Credit policy</x:v>
       </x:c>
       <x:c r="D53" s="28" t="str">
         <x:v>Alder Ridge</x:v>
       </x:c>
       <x:c r="E53" s="28" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>LTM 2026-06-30</x:v>
       </x:c>
       <x:c r="F53" s="28" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G53" s="28" t="str">
-        <x:v>Existing revolver</x:v>
+        <x:v>Minimum fixed-charge coverage</x:v>
       </x:c>
       <x:c r="H53" s="31" t="n">
-        <x:v>4900</x:v>
+        <x:v>1.35</x:v>
       </x:c>
       <x:c r="I53" s="28" t="str"/>
       <x:c r="J53" s="28" t="str">
-        <x:v>USD thousands</x:v>
+        <x:v>multiple</x:v>
       </x:c>
       <x:c r="K53" s="28" t="str">
         <x:v>Finance operating schedule</x:v>
@@ -17091,28 +17091,28 @@
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="37" t="str">
-        <x:v>TRY-00736</x:v>
+        <x:v>TRY-00456</x:v>
       </x:c>
       <x:c r="B54" s="28" t="str">
-        <x:v>ABL borrowing base and covenant cure</x:v>
+        <x:v>Credit metrics and incremental debt capacity</x:v>
       </x:c>
       <x:c r="C54" s="28" t="str">
-        <x:v>ABL covenant inputs</x:v>
+        <x:v>Credit policy</x:v>
       </x:c>
       <x:c r="D54" s="28" t="str">
         <x:v>Alder Ridge</x:v>
       </x:c>
       <x:c r="E54" s="28" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>LTM 2026-06-30</x:v>
       </x:c>
       <x:c r="F54" s="28" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G54" s="28" t="str">
-        <x:v>Availability block</x:v>
+        <x:v>Internal ratings debt cap</x:v>
       </x:c>
       <x:c r="H54" s="31" t="n">
-        <x:v>750000</x:v>
+        <x:v>12000000</x:v>
       </x:c>
       <x:c r="I54" s="28" t="str"/>
       <x:c r="J54" s="28" t="str">
@@ -17128,32 +17128,32 @@
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="37" t="str">
-        <x:v>TRY-00737</x:v>
+        <x:v>TRY-00457</x:v>
       </x:c>
       <x:c r="B55" s="28" t="str">
-        <x:v>ABL borrowing base and covenant cure</x:v>
+        <x:v>Credit metrics and incremental debt capacity</x:v>
       </x:c>
       <x:c r="C55" s="28" t="str">
-        <x:v>ABL covenant inputs</x:v>
+        <x:v>Credit policy</x:v>
       </x:c>
       <x:c r="D55" s="28" t="str">
         <x:v>Alder Ridge</x:v>
       </x:c>
       <x:c r="E55" s="28" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>LTM 2026-06-30</x:v>
       </x:c>
       <x:c r="F55" s="28" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G55" s="28" t="str">
-        <x:v>Minimum excess availability</x:v>
+        <x:v>Incremental debt interest rate</x:v>
       </x:c>
       <x:c r="H55" s="31" t="n">
-        <x:v>1500000</x:v>
+        <x:v>0.075</x:v>
       </x:c>
       <x:c r="I55" s="28" t="str"/>
       <x:c r="J55" s="28" t="str">
-        <x:v>USD</x:v>
+        <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K55" s="28" t="str">
         <x:v>Finance operating schedule</x:v>
@@ -17171,10 +17171,10 @@
         <x:v>ABL borrowing base and covenant cure</x:v>
       </x:c>
       <x:c r="C56" s="28" t="str">
-        <x:v>ABL covenant inputs</x:v>
+        <x:v>ABL borrowing base</x:v>
       </x:c>
       <x:c r="D56" s="28" t="str">
-        <x:v>Alder Ridge</x:v>
+        <x:v>Eligible accounts receivable</x:v>
       </x:c>
       <x:c r="E56" s="28" t="str">
         <x:v>2026-06-30</x:v>
@@ -17183,14 +17183,14 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G56" s="28" t="str">
-        <x:v>Minimum fixed charge coverage</x:v>
+        <x:v>Gross eligible collateral</x:v>
       </x:c>
       <x:c r="H56" s="31" t="n">
-        <x:v>1.2</x:v>
+        <x:v>11850000</x:v>
       </x:c>
       <x:c r="I56" s="28" t="str"/>
       <x:c r="J56" s="28" t="str">
-        <x:v>multiple</x:v>
+        <x:v>USD</x:v>
       </x:c>
       <x:c r="K56" s="28" t="str">
         <x:v>Finance operating schedule</x:v>
@@ -17208,10 +17208,10 @@
         <x:v>ABL borrowing base and covenant cure</x:v>
       </x:c>
       <x:c r="C57" s="28" t="str">
-        <x:v>ABL covenant inputs</x:v>
+        <x:v>ABL borrowing base</x:v>
       </x:c>
       <x:c r="D57" s="28" t="str">
-        <x:v>Alder Ridge</x:v>
+        <x:v>Eligible accounts receivable</x:v>
       </x:c>
       <x:c r="E57" s="28" t="str">
         <x:v>2026-06-30</x:v>
@@ -17220,14 +17220,14 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G57" s="28" t="str">
-        <x:v>EBITDA</x:v>
+        <x:v>Advance rate</x:v>
       </x:c>
       <x:c r="H57" s="31" t="n">
-        <x:v>5100</x:v>
+        <x:v>0.85</x:v>
       </x:c>
       <x:c r="I57" s="28" t="str"/>
       <x:c r="J57" s="28" t="str">
-        <x:v>USD thousands</x:v>
+        <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K57" s="28" t="str">
         <x:v>Finance operating schedule</x:v>
@@ -17245,10 +17245,10 @@
         <x:v>ABL borrowing base and covenant cure</x:v>
       </x:c>
       <x:c r="C58" s="28" t="str">
-        <x:v>ABL covenant inputs</x:v>
+        <x:v>ABL borrowing base</x:v>
       </x:c>
       <x:c r="D58" s="28" t="str">
-        <x:v>Alder Ridge</x:v>
+        <x:v>Eligible accounts receivable</x:v>
       </x:c>
       <x:c r="E58" s="28" t="str">
         <x:v>2026-06-30</x:v>
@@ -17257,10 +17257,10 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G58" s="28" t="str">
-        <x:v>Cash interest</x:v>
+        <x:v>Specific reserve</x:v>
       </x:c>
       <x:c r="H58" s="31" t="n">
-        <x:v>660000</x:v>
+        <x:v>1420000</x:v>
       </x:c>
       <x:c r="I58" s="28" t="str"/>
       <x:c r="J58" s="28" t="str">
@@ -17282,10 +17282,10 @@
         <x:v>ABL borrowing base and covenant cure</x:v>
       </x:c>
       <x:c r="C59" s="28" t="str">
-        <x:v>ABL covenant inputs</x:v>
+        <x:v>ABL borrowing base</x:v>
       </x:c>
       <x:c r="D59" s="28" t="str">
-        <x:v>Alder Ridge</x:v>
+        <x:v>Eligible inventory</x:v>
       </x:c>
       <x:c r="E59" s="28" t="str">
         <x:v>2026-06-30</x:v>
@@ -17294,14 +17294,14 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G59" s="28" t="str">
-        <x:v>Scheduled principal</x:v>
+        <x:v>Gross eligible collateral</x:v>
       </x:c>
       <x:c r="H59" s="31" t="n">
-        <x:v>820000</x:v>
+        <x:v>3600</x:v>
       </x:c>
       <x:c r="I59" s="28" t="str"/>
       <x:c r="J59" s="28" t="str">
-        <x:v>USD</x:v>
+        <x:v>USD thousands</x:v>
       </x:c>
       <x:c r="K59" s="28" t="str">
         <x:v>Finance operating schedule</x:v>
@@ -17319,10 +17319,10 @@
         <x:v>ABL borrowing base and covenant cure</x:v>
       </x:c>
       <x:c r="C60" s="28" t="str">
-        <x:v>ABL covenant inputs</x:v>
+        <x:v>ABL borrowing base</x:v>
       </x:c>
       <x:c r="D60" s="28" t="str">
-        <x:v>Alder Ridge</x:v>
+        <x:v>Eligible inventory</x:v>
       </x:c>
       <x:c r="E60" s="28" t="str">
         <x:v>2026-06-30</x:v>
@@ -17331,14 +17331,14 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G60" s="28" t="str">
-        <x:v>Cash taxes</x:v>
+        <x:v>Advance rate</x:v>
       </x:c>
       <x:c r="H60" s="31" t="n">
-        <x:v>520000</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="I60" s="28" t="str"/>
       <x:c r="J60" s="28" t="str">
-        <x:v>USD</x:v>
+        <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K60" s="28" t="str">
         <x:v>Finance operating schedule</x:v>
@@ -17356,10 +17356,10 @@
         <x:v>ABL borrowing base and covenant cure</x:v>
       </x:c>
       <x:c r="C61" s="28" t="str">
-        <x:v>ABL covenant inputs</x:v>
+        <x:v>ABL borrowing base</x:v>
       </x:c>
       <x:c r="D61" s="28" t="str">
-        <x:v>Alder Ridge</x:v>
+        <x:v>Eligible inventory</x:v>
       </x:c>
       <x:c r="E61" s="28" t="str">
         <x:v>2026-06-30</x:v>
@@ -17368,14 +17368,14 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G61" s="28" t="str">
-        <x:v>Unfinanced capex</x:v>
+        <x:v>Specific reserve</x:v>
       </x:c>
       <x:c r="H61" s="31" t="n">
-        <x:v>3200</x:v>
+        <x:v>440000</x:v>
       </x:c>
       <x:c r="I61" s="28" t="str"/>
       <x:c r="J61" s="28" t="str">
-        <x:v>USD thousands</x:v>
+        <x:v>USD</x:v>
       </x:c>
       <x:c r="K61" s="28" t="str">
         <x:v>Finance operating schedule</x:v>
@@ -17393,10 +17393,10 @@
         <x:v>ABL borrowing base and covenant cure</x:v>
       </x:c>
       <x:c r="C62" s="28" t="str">
-        <x:v>ABL covenant inputs</x:v>
+        <x:v>ABL borrowing base</x:v>
       </x:c>
       <x:c r="D62" s="28" t="str">
-        <x:v>Alder Ridge</x:v>
+        <x:v>Eligible equipment</x:v>
       </x:c>
       <x:c r="E62" s="28" t="str">
         <x:v>2026-06-30</x:v>
@@ -17405,10 +17405,10 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G62" s="28" t="str">
-        <x:v>Approved equity cure</x:v>
+        <x:v>Gross eligible collateral</x:v>
       </x:c>
       <x:c r="H62" s="31" t="n">
-        <x:v>625000</x:v>
+        <x:v>5200000</x:v>
       </x:c>
       <x:c r="I62" s="28" t="str"/>
       <x:c r="J62" s="28" t="str">
@@ -17424,16 +17424,16 @@
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="37" t="str">
-        <x:v>TRY-00759</x:v>
+        <x:v>TRY-00745</x:v>
       </x:c>
       <x:c r="B63" s="28" t="str">
         <x:v>ABL borrowing base and covenant cure</x:v>
       </x:c>
       <x:c r="C63" s="28" t="str">
-        <x:v>Detailed AR collateral control</x:v>
+        <x:v>ABL borrowing base</x:v>
       </x:c>
       <x:c r="D63" s="28" t="str">
-        <x:v>Cedar Medical</x:v>
+        <x:v>Eligible equipment</x:v>
       </x:c>
       <x:c r="E63" s="28" t="str">
         <x:v>2026-06-30</x:v>
@@ -17442,14 +17442,14 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G63" s="28" t="str">
-        <x:v>Gross receivable</x:v>
+        <x:v>Advance rate</x:v>
       </x:c>
       <x:c r="H63" s="31" t="n">
-        <x:v>2400000</x:v>
+        <x:v>0.35</x:v>
       </x:c>
       <x:c r="I63" s="28" t="str"/>
       <x:c r="J63" s="28" t="str">
-        <x:v>USD</x:v>
+        <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K63" s="28" t="str">
         <x:v>Finance operating schedule</x:v>
@@ -17461,16 +17461,16 @@
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="37" t="str">
-        <x:v>TRY-00760</x:v>
+        <x:v>TRY-00746</x:v>
       </x:c>
       <x:c r="B64" s="28" t="str">
         <x:v>ABL borrowing base and covenant cure</x:v>
       </x:c>
       <x:c r="C64" s="28" t="str">
-        <x:v>Detailed AR collateral control</x:v>
+        <x:v>ABL borrowing base</x:v>
       </x:c>
       <x:c r="D64" s="28" t="str">
-        <x:v>Cedar Medical</x:v>
+        <x:v>Eligible equipment</x:v>
       </x:c>
       <x:c r="E64" s="28" t="str">
         <x:v>2026-06-30</x:v>
@@ -17479,10 +17479,10 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G64" s="28" t="str">
-        <x:v>Over 90 days</x:v>
+        <x:v>Specific reserve</x:v>
       </x:c>
       <x:c r="H64" s="31" t="n">
-        <x:v>100000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I64" s="28" t="str"/>
       <x:c r="J64" s="28" t="str">
@@ -17498,16 +17498,16 @@
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="37" t="str">
-        <x:v>TRY-00761</x:v>
+        <x:v>TRY-00747</x:v>
       </x:c>
       <x:c r="B65" s="28" t="str">
         <x:v>ABL borrowing base and covenant cure</x:v>
       </x:c>
       <x:c r="C65" s="28" t="str">
-        <x:v>Detailed AR collateral control</x:v>
+        <x:v>ABL eligibility exclusions</x:v>
       </x:c>
       <x:c r="D65" s="28" t="str">
-        <x:v>Cedar Medical</x:v>
+        <x:v>AR over 90 days</x:v>
       </x:c>
       <x:c r="E65" s="28" t="str">
         <x:v>2026-06-30</x:v>
@@ -17516,10 +17516,10 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G65" s="28" t="str">
-        <x:v>Cross-aged exclusion</x:v>
+        <x:v>Excluded amount</x:v>
       </x:c>
       <x:c r="H65" s="31" t="n">
-        <x:v>0</x:v>
+        <x:v>760000</x:v>
       </x:c>
       <x:c r="I65" s="28" t="str"/>
       <x:c r="J65" s="28" t="str">
@@ -17535,16 +17535,16 @@
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="37" t="str">
-        <x:v>TRY-00762</x:v>
+        <x:v>TRY-00748</x:v>
       </x:c>
       <x:c r="B66" s="28" t="str">
         <x:v>ABL borrowing base and covenant cure</x:v>
       </x:c>
       <x:c r="C66" s="28" t="str">
-        <x:v>Detailed AR collateral control</x:v>
+        <x:v>ABL eligibility exclusions</x:v>
       </x:c>
       <x:c r="D66" s="28" t="str">
-        <x:v>Cedar Medical</x:v>
+        <x:v>Cross-aged customers</x:v>
       </x:c>
       <x:c r="E66" s="28" t="str">
         <x:v>2026-06-30</x:v>
@@ -17553,10 +17553,10 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G66" s="28" t="str">
-        <x:v>Related-party exclusion</x:v>
+        <x:v>Excluded amount</x:v>
       </x:c>
       <x:c r="H66" s="31" t="n">
-        <x:v>0</x:v>
+        <x:v>540000</x:v>
       </x:c>
       <x:c r="I66" s="28" t="str"/>
       <x:c r="J66" s="28" t="str">
@@ -17572,16 +17572,16 @@
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="37" t="str">
-        <x:v>TRY-00763</x:v>
+        <x:v>TRY-00749</x:v>
       </x:c>
       <x:c r="B67" s="28" t="str">
         <x:v>ABL borrowing base and covenant cure</x:v>
       </x:c>
       <x:c r="C67" s="28" t="str">
-        <x:v>Detailed AR collateral control</x:v>
+        <x:v>ABL eligibility exclusions</x:v>
       </x:c>
       <x:c r="D67" s="28" t="str">
-        <x:v>Helix Data Center</x:v>
+        <x:v>Related-party AR</x:v>
       </x:c>
       <x:c r="E67" s="28" t="str">
         <x:v>2026-06-30</x:v>
@@ -17590,14 +17590,14 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G67" s="28" t="str">
-        <x:v>Gross receivable</x:v>
+        <x:v>Excluded amount</x:v>
       </x:c>
       <x:c r="H67" s="31" t="n">
-        <x:v>3100000</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="I67" s="28" t="str"/>
       <x:c r="J67" s="28" t="str">
-        <x:v>USD</x:v>
+        <x:v>USD thousands</x:v>
       </x:c>
       <x:c r="K67" s="28" t="str">
         <x:v>Finance operating schedule</x:v>
@@ -17609,16 +17609,16 @@
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="37" t="str">
-        <x:v>TRY-00764</x:v>
+        <x:v>TRY-00750</x:v>
       </x:c>
       <x:c r="B68" s="28" t="str">
         <x:v>ABL borrowing base and covenant cure</x:v>
       </x:c>
       <x:c r="C68" s="28" t="str">
-        <x:v>Detailed AR collateral control</x:v>
+        <x:v>ABL eligibility exclusions</x:v>
       </x:c>
       <x:c r="D68" s="28" t="str">
-        <x:v>Helix Data Center</x:v>
+        <x:v>Obsolete inventory</x:v>
       </x:c>
       <x:c r="E68" s="28" t="str">
         <x:v>2026-06-30</x:v>
@@ -17627,10 +17627,10 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G68" s="28" t="str">
-        <x:v>Over 90 days</x:v>
+        <x:v>Excluded amount</x:v>
       </x:c>
       <x:c r="H68" s="31" t="n">
-        <x:v>650000</x:v>
+        <x:v>390000</x:v>
       </x:c>
       <x:c r="I68" s="28" t="str"/>
       <x:c r="J68" s="28" t="str">
@@ -17646,16 +17646,16 @@
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="37" t="str">
-        <x:v>TRY-00765</x:v>
+        <x:v>TRY-00751</x:v>
       </x:c>
       <x:c r="B69" s="28" t="str">
         <x:v>ABL borrowing base and covenant cure</x:v>
       </x:c>
       <x:c r="C69" s="28" t="str">
-        <x:v>Detailed AR collateral control</x:v>
+        <x:v>ABL covenant inputs</x:v>
       </x:c>
       <x:c r="D69" s="28" t="str">
-        <x:v>Helix Data Center</x:v>
+        <x:v>Alder Ridge</x:v>
       </x:c>
       <x:c r="E69" s="28" t="str">
         <x:v>2026-06-30</x:v>
@@ -17664,10 +17664,10 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G69" s="28" t="str">
-        <x:v>Cross-aged exclusion</x:v>
+        <x:v>Facility commitment</x:v>
       </x:c>
       <x:c r="H69" s="31" t="n">
-        <x:v>0</x:v>
+        <x:v>12000000</x:v>
       </x:c>
       <x:c r="I69" s="28" t="str"/>
       <x:c r="J69" s="28" t="str">
@@ -17683,16 +17683,16 @@
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="37" t="str">
-        <x:v>TRY-00766</x:v>
+        <x:v>TRY-00752</x:v>
       </x:c>
       <x:c r="B70" s="28" t="str">
         <x:v>ABL borrowing base and covenant cure</x:v>
       </x:c>
       <x:c r="C70" s="28" t="str">
-        <x:v>Detailed AR collateral control</x:v>
+        <x:v>ABL covenant inputs</x:v>
       </x:c>
       <x:c r="D70" s="28" t="str">
-        <x:v>Helix Data Center</x:v>
+        <x:v>Alder Ridge</x:v>
       </x:c>
       <x:c r="E70" s="28" t="str">
         <x:v>2026-06-30</x:v>
@@ -17701,10 +17701,10 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G70" s="28" t="str">
-        <x:v>Related-party exclusion</x:v>
+        <x:v>Existing letters of credit</x:v>
       </x:c>
       <x:c r="H70" s="31" t="n">
-        <x:v>0</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="I70" s="28" t="str"/>
       <x:c r="J70" s="28" t="str">
@@ -17720,16 +17720,16 @@
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="37" t="str">
-        <x:v>TRY-00767</x:v>
+        <x:v>TRY-00753</x:v>
       </x:c>
       <x:c r="B71" s="28" t="str">
         <x:v>ABL borrowing base and covenant cure</x:v>
       </x:c>
       <x:c r="C71" s="28" t="str">
-        <x:v>Detailed AR collateral control</x:v>
+        <x:v>ABL covenant inputs</x:v>
       </x:c>
       <x:c r="D71" s="28" t="str">
-        <x:v>Portland Schools</x:v>
+        <x:v>Alder Ridge</x:v>
       </x:c>
       <x:c r="E71" s="28" t="str">
         <x:v>2026-06-30</x:v>
@@ -17738,14 +17738,14 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G71" s="28" t="str">
-        <x:v>Gross receivable</x:v>
+        <x:v>Existing revolver</x:v>
       </x:c>
       <x:c r="H71" s="31" t="n">
-        <x:v>2200000</x:v>
+        <x:v>4900</x:v>
       </x:c>
       <x:c r="I71" s="28" t="str"/>
       <x:c r="J71" s="28" t="str">
-        <x:v>USD</x:v>
+        <x:v>USD thousands</x:v>
       </x:c>
       <x:c r="K71" s="28" t="str">
         <x:v>Finance operating schedule</x:v>
@@ -17757,16 +17757,16 @@
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="37" t="str">
-        <x:v>TRY-00768</x:v>
+        <x:v>TRY-00754</x:v>
       </x:c>
       <x:c r="B72" s="28" t="str">
         <x:v>ABL borrowing base and covenant cure</x:v>
       </x:c>
       <x:c r="C72" s="28" t="str">
-        <x:v>Detailed AR collateral control</x:v>
+        <x:v>ABL covenant inputs</x:v>
       </x:c>
       <x:c r="D72" s="28" t="str">
-        <x:v>Portland Schools</x:v>
+        <x:v>Alder Ridge</x:v>
       </x:c>
       <x:c r="E72" s="28" t="str">
         <x:v>2026-06-30</x:v>
@@ -17775,10 +17775,10 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G72" s="28" t="str">
-        <x:v>Over 90 days</x:v>
+        <x:v>Availability block</x:v>
       </x:c>
       <x:c r="H72" s="31" t="n">
-        <x:v>0</x:v>
+        <x:v>750000</x:v>
       </x:c>
       <x:c r="I72" s="28" t="str"/>
       <x:c r="J72" s="28" t="str">
@@ -17794,16 +17794,16 @@
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="37" t="str">
-        <x:v>TRY-00769</x:v>
+        <x:v>TRY-00755</x:v>
       </x:c>
       <x:c r="B73" s="28" t="str">
         <x:v>ABL borrowing base and covenant cure</x:v>
       </x:c>
       <x:c r="C73" s="28" t="str">
-        <x:v>Detailed AR collateral control</x:v>
+        <x:v>ABL covenant inputs</x:v>
       </x:c>
       <x:c r="D73" s="28" t="str">
-        <x:v>Portland Schools</x:v>
+        <x:v>Alder Ridge</x:v>
       </x:c>
       <x:c r="E73" s="28" t="str">
         <x:v>2026-06-30</x:v>
@@ -17812,10 +17812,10 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G73" s="28" t="str">
-        <x:v>Cross-aged exclusion</x:v>
+        <x:v>Minimum excess availability</x:v>
       </x:c>
       <x:c r="H73" s="31" t="n">
-        <x:v>0</x:v>
+        <x:v>1500000</x:v>
       </x:c>
       <x:c r="I73" s="28" t="str"/>
       <x:c r="J73" s="28" t="str">
@@ -17831,16 +17831,16 @@
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="37" t="str">
-        <x:v>TRY-00770</x:v>
+        <x:v>TRY-00756</x:v>
       </x:c>
       <x:c r="B74" s="28" t="str">
         <x:v>ABL borrowing base and covenant cure</x:v>
       </x:c>
       <x:c r="C74" s="28" t="str">
-        <x:v>Detailed AR collateral control</x:v>
+        <x:v>ABL covenant inputs</x:v>
       </x:c>
       <x:c r="D74" s="28" t="str">
-        <x:v>Portland Schools</x:v>
+        <x:v>Alder Ridge</x:v>
       </x:c>
       <x:c r="E74" s="28" t="str">
         <x:v>2026-06-30</x:v>
@@ -17849,14 +17849,14 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G74" s="28" t="str">
-        <x:v>Related-party exclusion</x:v>
+        <x:v>Minimum fixed charge coverage</x:v>
       </x:c>
       <x:c r="H74" s="31" t="n">
-        <x:v>0</x:v>
+        <x:v>1.2</x:v>
       </x:c>
       <x:c r="I74" s="28" t="str"/>
       <x:c r="J74" s="28" t="str">
-        <x:v>USD</x:v>
+        <x:v>multiple</x:v>
       </x:c>
       <x:c r="K74" s="28" t="str">
         <x:v>Finance operating schedule</x:v>
@@ -17868,16 +17868,16 @@
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="37" t="str">
-        <x:v>TRY-00771</x:v>
+        <x:v>TRY-00757</x:v>
       </x:c>
       <x:c r="B75" s="28" t="str">
         <x:v>ABL borrowing base and covenant cure</x:v>
       </x:c>
       <x:c r="C75" s="28" t="str">
-        <x:v>Detailed AR collateral control</x:v>
+        <x:v>ABL covenant inputs</x:v>
       </x:c>
       <x:c r="D75" s="28" t="str">
-        <x:v>Juniper Offices</x:v>
+        <x:v>Alder Ridge</x:v>
       </x:c>
       <x:c r="E75" s="28" t="str">
         <x:v>2026-06-30</x:v>
@@ -17886,14 +17886,14 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G75" s="28" t="str">
-        <x:v>Gross receivable</x:v>
+        <x:v>EBITDA</x:v>
       </x:c>
       <x:c r="H75" s="31" t="n">
-        <x:v>1800000</x:v>
+        <x:v>5100</x:v>
       </x:c>
       <x:c r="I75" s="28" t="str"/>
       <x:c r="J75" s="28" t="str">
-        <x:v>USD</x:v>
+        <x:v>USD thousands</x:v>
       </x:c>
       <x:c r="K75" s="28" t="str">
         <x:v>Finance operating schedule</x:v>
@@ -17905,16 +17905,16 @@
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="37" t="str">
-        <x:v>TRY-00772</x:v>
+        <x:v>TRY-00758</x:v>
       </x:c>
       <x:c r="B76" s="28" t="str">
         <x:v>ABL borrowing base and covenant cure</x:v>
       </x:c>
       <x:c r="C76" s="28" t="str">
-        <x:v>Detailed AR collateral control</x:v>
+        <x:v>ABL covenant inputs</x:v>
       </x:c>
       <x:c r="D76" s="28" t="str">
-        <x:v>Juniper Offices</x:v>
+        <x:v>Alder Ridge</x:v>
       </x:c>
       <x:c r="E76" s="28" t="str">
         <x:v>2026-06-30</x:v>
@@ -17923,10 +17923,10 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G76" s="28" t="str">
-        <x:v>Over 90 days</x:v>
+        <x:v>Cash interest</x:v>
       </x:c>
       <x:c r="H76" s="31" t="n">
-        <x:v>300000</x:v>
+        <x:v>660000</x:v>
       </x:c>
       <x:c r="I76" s="28" t="str"/>
       <x:c r="J76" s="28" t="str">
@@ -17942,16 +17942,16 @@
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="37" t="str">
-        <x:v>TRY-00773</x:v>
+        <x:v>TRY-00759</x:v>
       </x:c>
       <x:c r="B77" s="28" t="str">
         <x:v>ABL borrowing base and covenant cure</x:v>
       </x:c>
       <x:c r="C77" s="28" t="str">
-        <x:v>Detailed AR collateral control</x:v>
+        <x:v>ABL covenant inputs</x:v>
       </x:c>
       <x:c r="D77" s="28" t="str">
-        <x:v>Juniper Offices</x:v>
+        <x:v>Alder Ridge</x:v>
       </x:c>
       <x:c r="E77" s="28" t="str">
         <x:v>2026-06-30</x:v>
@@ -17960,10 +17960,10 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G77" s="28" t="str">
-        <x:v>Cross-aged exclusion</x:v>
+        <x:v>Scheduled principal</x:v>
       </x:c>
       <x:c r="H77" s="31" t="n">
-        <x:v>0</x:v>
+        <x:v>820000</x:v>
       </x:c>
       <x:c r="I77" s="28" t="str"/>
       <x:c r="J77" s="28" t="str">
@@ -17979,16 +17979,16 @@
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="37" t="str">
-        <x:v>TRY-00774</x:v>
+        <x:v>TRY-00760</x:v>
       </x:c>
       <x:c r="B78" s="28" t="str">
         <x:v>ABL borrowing base and covenant cure</x:v>
       </x:c>
       <x:c r="C78" s="28" t="str">
-        <x:v>Detailed AR collateral control</x:v>
+        <x:v>ABL covenant inputs</x:v>
       </x:c>
       <x:c r="D78" s="28" t="str">
-        <x:v>Juniper Offices</x:v>
+        <x:v>Alder Ridge</x:v>
       </x:c>
       <x:c r="E78" s="28" t="str">
         <x:v>2026-06-30</x:v>
@@ -17997,10 +17997,10 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G78" s="28" t="str">
-        <x:v>Related-party exclusion</x:v>
+        <x:v>Cash taxes</x:v>
       </x:c>
       <x:c r="H78" s="31" t="n">
-        <x:v>0</x:v>
+        <x:v>520000</x:v>
       </x:c>
       <x:c r="I78" s="28" t="str"/>
       <x:c r="J78" s="28" t="str">
@@ -18016,16 +18016,16 @@
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="37" t="str">
-        <x:v>TRY-00775</x:v>
+        <x:v>TRY-00761</x:v>
       </x:c>
       <x:c r="B79" s="28" t="str">
         <x:v>ABL borrowing base and covenant cure</x:v>
       </x:c>
       <x:c r="C79" s="28" t="str">
-        <x:v>Detailed AR collateral control</x:v>
+        <x:v>ABL covenant inputs</x:v>
       </x:c>
       <x:c r="D79" s="28" t="str">
-        <x:v>Cascade Retail</x:v>
+        <x:v>Alder Ridge</x:v>
       </x:c>
       <x:c r="E79" s="28" t="str">
         <x:v>2026-06-30</x:v>
@@ -18034,14 +18034,14 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G79" s="28" t="str">
-        <x:v>Gross receivable</x:v>
+        <x:v>Unfinanced capex</x:v>
       </x:c>
       <x:c r="H79" s="31" t="n">
-        <x:v>1600000</x:v>
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="I79" s="28" t="str"/>
       <x:c r="J79" s="28" t="str">
-        <x:v>USD</x:v>
+        <x:v>USD thousands</x:v>
       </x:c>
       <x:c r="K79" s="28" t="str">
         <x:v>Finance operating schedule</x:v>
@@ -18053,16 +18053,16 @@
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="37" t="str">
-        <x:v>TRY-00776</x:v>
+        <x:v>TRY-00762</x:v>
       </x:c>
       <x:c r="B80" s="28" t="str">
         <x:v>ABL borrowing base and covenant cure</x:v>
       </x:c>
       <x:c r="C80" s="28" t="str">
-        <x:v>Detailed AR collateral control</x:v>
+        <x:v>ABL covenant inputs</x:v>
       </x:c>
       <x:c r="D80" s="28" t="str">
-        <x:v>Cascade Retail</x:v>
+        <x:v>Alder Ridge</x:v>
       </x:c>
       <x:c r="E80" s="28" t="str">
         <x:v>2026-06-30</x:v>
@@ -18071,10 +18071,10 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G80" s="28" t="str">
-        <x:v>Over 90 days</x:v>
+        <x:v>Approved equity cure</x:v>
       </x:c>
       <x:c r="H80" s="31" t="n">
-        <x:v>0</x:v>
+        <x:v>625000</x:v>
       </x:c>
       <x:c r="I80" s="28" t="str"/>
       <x:c r="J80" s="28" t="str">
@@ -18099,7 +18099,7 @@
         <x:v>Detailed AR collateral control</x:v>
       </x:c>
       <x:c r="D81" s="28" t="str">
-        <x:v>Cascade Retail</x:v>
+        <x:v>Cedar Medical</x:v>
       </x:c>
       <x:c r="E81" s="28" t="str">
         <x:v>2026-06-30</x:v>
@@ -18108,10 +18108,10 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G81" s="28" t="str">
-        <x:v>Cross-aged exclusion</x:v>
+        <x:v>Gross receivable</x:v>
       </x:c>
       <x:c r="H81" s="31" t="n">
-        <x:v>500000</x:v>
+        <x:v>2400000</x:v>
       </x:c>
       <x:c r="I81" s="28" t="str"/>
       <x:c r="J81" s="28" t="str">
@@ -18136,7 +18136,7 @@
         <x:v>Detailed AR collateral control</x:v>
       </x:c>
       <x:c r="D82" s="28" t="str">
-        <x:v>Cascade Retail</x:v>
+        <x:v>Cedar Medical</x:v>
       </x:c>
       <x:c r="E82" s="28" t="str">
         <x:v>2026-06-30</x:v>
@@ -18145,10 +18145,10 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G82" s="28" t="str">
-        <x:v>Related-party exclusion</x:v>
+        <x:v>Over 90 days</x:v>
       </x:c>
       <x:c r="H82" s="31" t="n">
-        <x:v>0</x:v>
+        <x:v>100000</x:v>
       </x:c>
       <x:c r="I82" s="28" t="str"/>
       <x:c r="J82" s="28" t="str">
@@ -18173,7 +18173,7 @@
         <x:v>Detailed AR collateral control</x:v>
       </x:c>
       <x:c r="D83" s="28" t="str">
-        <x:v>Other and affiliate</x:v>
+        <x:v>Cedar Medical</x:v>
       </x:c>
       <x:c r="E83" s="28" t="str">
         <x:v>2026-06-30</x:v>
@@ -18182,10 +18182,10 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G83" s="28" t="str">
-        <x:v>Gross receivable</x:v>
+        <x:v>Cross-aged exclusion</x:v>
       </x:c>
       <x:c r="H83" s="31" t="n">
-        <x:v>1400000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I83" s="28" t="str"/>
       <x:c r="J83" s="28" t="str">
@@ -18210,7 +18210,7 @@
         <x:v>Detailed AR collateral control</x:v>
       </x:c>
       <x:c r="D84" s="28" t="str">
-        <x:v>Other and affiliate</x:v>
+        <x:v>Cedar Medical</x:v>
       </x:c>
       <x:c r="E84" s="28" t="str">
         <x:v>2026-06-30</x:v>
@@ -18219,7 +18219,7 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G84" s="28" t="str">
-        <x:v>Over 90 days</x:v>
+        <x:v>Related-party exclusion</x:v>
       </x:c>
       <x:c r="H84" s="31" t="n">
         <x:v>0</x:v>
@@ -18247,7 +18247,7 @@
         <x:v>Detailed AR collateral control</x:v>
       </x:c>
       <x:c r="D85" s="28" t="str">
-        <x:v>Other and affiliate</x:v>
+        <x:v>Helix Data Center</x:v>
       </x:c>
       <x:c r="E85" s="28" t="str">
         <x:v>2026-06-30</x:v>
@@ -18256,10 +18256,10 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G85" s="28" t="str">
-        <x:v>Cross-aged exclusion</x:v>
+        <x:v>Gross receivable</x:v>
       </x:c>
       <x:c r="H85" s="31" t="n">
-        <x:v>0</x:v>
+        <x:v>3100000</x:v>
       </x:c>
       <x:c r="I85" s="28" t="str"/>
       <x:c r="J85" s="28" t="str">
@@ -18284,7 +18284,7 @@
         <x:v>Detailed AR collateral control</x:v>
       </x:c>
       <x:c r="D86" s="28" t="str">
-        <x:v>Other and affiliate</x:v>
+        <x:v>Helix Data Center</x:v>
       </x:c>
       <x:c r="E86" s="28" t="str">
         <x:v>2026-06-30</x:v>
@@ -18293,14 +18293,14 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G86" s="28" t="str">
-        <x:v>Related-party exclusion</x:v>
+        <x:v>Over 90 days</x:v>
       </x:c>
       <x:c r="H86" s="31" t="n">
-        <x:v>220</x:v>
+        <x:v>650000</x:v>
       </x:c>
       <x:c r="I86" s="28" t="str"/>
       <x:c r="J86" s="28" t="str">
-        <x:v>USD thousands</x:v>
+        <x:v>USD</x:v>
       </x:c>
       <x:c r="K86" s="28" t="str">
         <x:v>Finance operating schedule</x:v>
@@ -18318,10 +18318,10 @@
         <x:v>ABL borrowing base and covenant cure</x:v>
       </x:c>
       <x:c r="C87" s="28" t="str">
-        <x:v>Detailed inventory collateral control</x:v>
+        <x:v>Detailed AR collateral control</x:v>
       </x:c>
       <x:c r="D87" s="28" t="str">
-        <x:v>Raw material</x:v>
+        <x:v>Helix Data Center</x:v>
       </x:c>
       <x:c r="E87" s="28" t="str">
         <x:v>2026-06-30</x:v>
@@ -18330,10 +18330,10 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G87" s="28" t="str">
-        <x:v>Gross inventory</x:v>
+        <x:v>Cross-aged exclusion</x:v>
       </x:c>
       <x:c r="H87" s="31" t="n">
-        <x:v>3000000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I87" s="28" t="str"/>
       <x:c r="J87" s="28" t="str">
@@ -18355,10 +18355,10 @@
         <x:v>ABL borrowing base and covenant cure</x:v>
       </x:c>
       <x:c r="C88" s="28" t="str">
-        <x:v>Detailed inventory collateral control</x:v>
+        <x:v>Detailed AR collateral control</x:v>
       </x:c>
       <x:c r="D88" s="28" t="str">
-        <x:v>Raw material</x:v>
+        <x:v>Helix Data Center</x:v>
       </x:c>
       <x:c r="E88" s="28" t="str">
         <x:v>2026-06-30</x:v>
@@ -18367,14 +18367,14 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G88" s="28" t="str">
-        <x:v>Eligibility factor</x:v>
+        <x:v>Related-party exclusion</x:v>
       </x:c>
       <x:c r="H88" s="31" t="n">
-        <x:v>0.95</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I88" s="28" t="str"/>
       <x:c r="J88" s="28" t="str">
-        <x:v>decimal ratio</x:v>
+        <x:v>USD</x:v>
       </x:c>
       <x:c r="K88" s="28" t="str">
         <x:v>Finance operating schedule</x:v>
@@ -18392,10 +18392,10 @@
         <x:v>ABL borrowing base and covenant cure</x:v>
       </x:c>
       <x:c r="C89" s="28" t="str">
-        <x:v>Detailed inventory collateral control</x:v>
+        <x:v>Detailed AR collateral control</x:v>
       </x:c>
       <x:c r="D89" s="28" t="str">
-        <x:v>Work in process</x:v>
+        <x:v>Portland Schools</x:v>
       </x:c>
       <x:c r="E89" s="28" t="str">
         <x:v>2026-06-30</x:v>
@@ -18404,10 +18404,10 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G89" s="28" t="str">
-        <x:v>Gross inventory</x:v>
+        <x:v>Gross receivable</x:v>
       </x:c>
       <x:c r="H89" s="31" t="n">
-        <x:v>1400000</x:v>
+        <x:v>2200000</x:v>
       </x:c>
       <x:c r="I89" s="28" t="str"/>
       <x:c r="J89" s="28" t="str">
@@ -18429,10 +18429,10 @@
         <x:v>ABL borrowing base and covenant cure</x:v>
       </x:c>
       <x:c r="C90" s="28" t="str">
-        <x:v>Detailed inventory collateral control</x:v>
+        <x:v>Detailed AR collateral control</x:v>
       </x:c>
       <x:c r="D90" s="28" t="str">
-        <x:v>Work in process</x:v>
+        <x:v>Portland Schools</x:v>
       </x:c>
       <x:c r="E90" s="28" t="str">
         <x:v>2026-06-30</x:v>
@@ -18441,14 +18441,14 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G90" s="28" t="str">
-        <x:v>Eligibility factor</x:v>
+        <x:v>Over 90 days</x:v>
       </x:c>
       <x:c r="H90" s="31" t="n">
-        <x:v>0.8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I90" s="28" t="str"/>
       <x:c r="J90" s="28" t="str">
-        <x:v>decimal ratio</x:v>
+        <x:v>USD</x:v>
       </x:c>
       <x:c r="K90" s="28" t="str">
         <x:v>Finance operating schedule</x:v>
@@ -18466,10 +18466,10 @@
         <x:v>ABL borrowing base and covenant cure</x:v>
       </x:c>
       <x:c r="C91" s="28" t="str">
-        <x:v>Detailed inventory collateral control</x:v>
+        <x:v>Detailed AR collateral control</x:v>
       </x:c>
       <x:c r="D91" s="28" t="str">
-        <x:v>Finished goods</x:v>
+        <x:v>Portland Schools</x:v>
       </x:c>
       <x:c r="E91" s="28" t="str">
         <x:v>2026-06-30</x:v>
@@ -18478,10 +18478,10 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G91" s="28" t="str">
-        <x:v>Gross inventory</x:v>
+        <x:v>Cross-aged exclusion</x:v>
       </x:c>
       <x:c r="H91" s="31" t="n">
-        <x:v>1100000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I91" s="28" t="str"/>
       <x:c r="J91" s="28" t="str">
@@ -18503,10 +18503,10 @@
         <x:v>ABL borrowing base and covenant cure</x:v>
       </x:c>
       <x:c r="C92" s="28" t="str">
-        <x:v>Detailed inventory collateral control</x:v>
+        <x:v>Detailed AR collateral control</x:v>
       </x:c>
       <x:c r="D92" s="28" t="str">
-        <x:v>Finished goods</x:v>
+        <x:v>Portland Schools</x:v>
       </x:c>
       <x:c r="E92" s="28" t="str">
         <x:v>2026-06-30</x:v>
@@ -18515,14 +18515,14 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G92" s="28" t="str">
-        <x:v>Eligibility factor</x:v>
+        <x:v>Related-party exclusion</x:v>
       </x:c>
       <x:c r="H92" s="31" t="n">
-        <x:v>0.7</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I92" s="28" t="str"/>
       <x:c r="J92" s="28" t="str">
-        <x:v>decimal ratio</x:v>
+        <x:v>USD</x:v>
       </x:c>
       <x:c r="K92" s="28" t="str">
         <x:v>Finance operating schedule</x:v>
@@ -18540,10 +18540,10 @@
         <x:v>ABL borrowing base and covenant cure</x:v>
       </x:c>
       <x:c r="C93" s="28" t="str">
-        <x:v>Detailed ABL policy</x:v>
+        <x:v>Detailed AR collateral control</x:v>
       </x:c>
       <x:c r="D93" s="28" t="str">
-        <x:v>Alder Ridge</x:v>
+        <x:v>Juniper Offices</x:v>
       </x:c>
       <x:c r="E93" s="28" t="str">
         <x:v>2026-06-30</x:v>
@@ -18552,59 +18552,725 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="G93" s="28" t="str">
-        <x:v>Single customer concentration cap</x:v>
+        <x:v>Gross receivable</x:v>
       </x:c>
       <x:c r="H93" s="31" t="n">
-        <x:v>0.2</x:v>
+        <x:v>1800000</x:v>
       </x:c>
       <x:c r="I93" s="28" t="str"/>
       <x:c r="J93" s="28" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="K93" s="28" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="L93" s="34" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="M93" s="28" t="str"/>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" s="37" t="str">
+        <x:v>TRY-00790</x:v>
+      </x:c>
+      <x:c r="B94" s="28" t="str">
+        <x:v>ABL borrowing base and covenant cure</x:v>
+      </x:c>
+      <x:c r="C94" s="28" t="str">
+        <x:v>Detailed AR collateral control</x:v>
+      </x:c>
+      <x:c r="D94" s="28" t="str">
+        <x:v>Juniper Offices</x:v>
+      </x:c>
+      <x:c r="E94" s="28" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="F94" s="28" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="G94" s="28" t="str">
+        <x:v>Over 90 days</x:v>
+      </x:c>
+      <x:c r="H94" s="31" t="n">
+        <x:v>300000</x:v>
+      </x:c>
+      <x:c r="I94" s="28" t="str"/>
+      <x:c r="J94" s="28" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="K94" s="28" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="L94" s="34" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="M94" s="28" t="str"/>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" s="37" t="str">
+        <x:v>TRY-00791</x:v>
+      </x:c>
+      <x:c r="B95" s="28" t="str">
+        <x:v>ABL borrowing base and covenant cure</x:v>
+      </x:c>
+      <x:c r="C95" s="28" t="str">
+        <x:v>Detailed AR collateral control</x:v>
+      </x:c>
+      <x:c r="D95" s="28" t="str">
+        <x:v>Juniper Offices</x:v>
+      </x:c>
+      <x:c r="E95" s="28" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="F95" s="28" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="G95" s="28" t="str">
+        <x:v>Cross-aged exclusion</x:v>
+      </x:c>
+      <x:c r="H95" s="31" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I95" s="28" t="str"/>
+      <x:c r="J95" s="28" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="K95" s="28" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="L95" s="34" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="M95" s="28" t="str"/>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" s="37" t="str">
+        <x:v>TRY-00792</x:v>
+      </x:c>
+      <x:c r="B96" s="28" t="str">
+        <x:v>ABL borrowing base and covenant cure</x:v>
+      </x:c>
+      <x:c r="C96" s="28" t="str">
+        <x:v>Detailed AR collateral control</x:v>
+      </x:c>
+      <x:c r="D96" s="28" t="str">
+        <x:v>Juniper Offices</x:v>
+      </x:c>
+      <x:c r="E96" s="28" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="F96" s="28" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="G96" s="28" t="str">
+        <x:v>Related-party exclusion</x:v>
+      </x:c>
+      <x:c r="H96" s="31" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I96" s="28" t="str"/>
+      <x:c r="J96" s="28" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="K96" s="28" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="L96" s="34" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="M96" s="28" t="str"/>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" s="37" t="str">
+        <x:v>TRY-00793</x:v>
+      </x:c>
+      <x:c r="B97" s="28" t="str">
+        <x:v>ABL borrowing base and covenant cure</x:v>
+      </x:c>
+      <x:c r="C97" s="28" t="str">
+        <x:v>Detailed AR collateral control</x:v>
+      </x:c>
+      <x:c r="D97" s="28" t="str">
+        <x:v>Cascade Retail</x:v>
+      </x:c>
+      <x:c r="E97" s="28" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="F97" s="28" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="G97" s="28" t="str">
+        <x:v>Gross receivable</x:v>
+      </x:c>
+      <x:c r="H97" s="31" t="n">
+        <x:v>1600000</x:v>
+      </x:c>
+      <x:c r="I97" s="28" t="str"/>
+      <x:c r="J97" s="28" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="K97" s="28" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="L97" s="34" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="M97" s="28" t="str"/>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" s="37" t="str">
+        <x:v>TRY-00794</x:v>
+      </x:c>
+      <x:c r="B98" s="28" t="str">
+        <x:v>ABL borrowing base and covenant cure</x:v>
+      </x:c>
+      <x:c r="C98" s="28" t="str">
+        <x:v>Detailed AR collateral control</x:v>
+      </x:c>
+      <x:c r="D98" s="28" t="str">
+        <x:v>Cascade Retail</x:v>
+      </x:c>
+      <x:c r="E98" s="28" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="F98" s="28" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="G98" s="28" t="str">
+        <x:v>Over 90 days</x:v>
+      </x:c>
+      <x:c r="H98" s="31" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I98" s="28" t="str"/>
+      <x:c r="J98" s="28" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="K98" s="28" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="L98" s="34" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="M98" s="28" t="str"/>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" s="37" t="str">
+        <x:v>TRY-00795</x:v>
+      </x:c>
+      <x:c r="B99" s="28" t="str">
+        <x:v>ABL borrowing base and covenant cure</x:v>
+      </x:c>
+      <x:c r="C99" s="28" t="str">
+        <x:v>Detailed AR collateral control</x:v>
+      </x:c>
+      <x:c r="D99" s="28" t="str">
+        <x:v>Cascade Retail</x:v>
+      </x:c>
+      <x:c r="E99" s="28" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="F99" s="28" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="G99" s="28" t="str">
+        <x:v>Cross-aged exclusion</x:v>
+      </x:c>
+      <x:c r="H99" s="31" t="n">
+        <x:v>500000</x:v>
+      </x:c>
+      <x:c r="I99" s="28" t="str"/>
+      <x:c r="J99" s="28" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="K99" s="28" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="L99" s="34" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="M99" s="28" t="str"/>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" s="37" t="str">
+        <x:v>TRY-00796</x:v>
+      </x:c>
+      <x:c r="B100" s="28" t="str">
+        <x:v>ABL borrowing base and covenant cure</x:v>
+      </x:c>
+      <x:c r="C100" s="28" t="str">
+        <x:v>Detailed AR collateral control</x:v>
+      </x:c>
+      <x:c r="D100" s="28" t="str">
+        <x:v>Cascade Retail</x:v>
+      </x:c>
+      <x:c r="E100" s="28" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="F100" s="28" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="G100" s="28" t="str">
+        <x:v>Related-party exclusion</x:v>
+      </x:c>
+      <x:c r="H100" s="31" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I100" s="28" t="str"/>
+      <x:c r="J100" s="28" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="K100" s="28" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="L100" s="34" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="M100" s="28" t="str"/>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" s="37" t="str">
+        <x:v>TRY-00797</x:v>
+      </x:c>
+      <x:c r="B101" s="28" t="str">
+        <x:v>ABL borrowing base and covenant cure</x:v>
+      </x:c>
+      <x:c r="C101" s="28" t="str">
+        <x:v>Detailed AR collateral control</x:v>
+      </x:c>
+      <x:c r="D101" s="28" t="str">
+        <x:v>Other and affiliate</x:v>
+      </x:c>
+      <x:c r="E101" s="28" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="F101" s="28" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="G101" s="28" t="str">
+        <x:v>Gross receivable</x:v>
+      </x:c>
+      <x:c r="H101" s="31" t="n">
+        <x:v>1400000</x:v>
+      </x:c>
+      <x:c r="I101" s="28" t="str"/>
+      <x:c r="J101" s="28" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="K101" s="28" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="L101" s="34" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="M101" s="28" t="str"/>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" s="37" t="str">
+        <x:v>TRY-00798</x:v>
+      </x:c>
+      <x:c r="B102" s="28" t="str">
+        <x:v>ABL borrowing base and covenant cure</x:v>
+      </x:c>
+      <x:c r="C102" s="28" t="str">
+        <x:v>Detailed AR collateral control</x:v>
+      </x:c>
+      <x:c r="D102" s="28" t="str">
+        <x:v>Other and affiliate</x:v>
+      </x:c>
+      <x:c r="E102" s="28" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="F102" s="28" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="G102" s="28" t="str">
+        <x:v>Over 90 days</x:v>
+      </x:c>
+      <x:c r="H102" s="31" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I102" s="28" t="str"/>
+      <x:c r="J102" s="28" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="K102" s="28" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="L102" s="34" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="M102" s="28" t="str"/>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" s="37" t="str">
+        <x:v>TRY-00799</x:v>
+      </x:c>
+      <x:c r="B103" s="28" t="str">
+        <x:v>ABL borrowing base and covenant cure</x:v>
+      </x:c>
+      <x:c r="C103" s="28" t="str">
+        <x:v>Detailed AR collateral control</x:v>
+      </x:c>
+      <x:c r="D103" s="28" t="str">
+        <x:v>Other and affiliate</x:v>
+      </x:c>
+      <x:c r="E103" s="28" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="F103" s="28" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="G103" s="28" t="str">
+        <x:v>Cross-aged exclusion</x:v>
+      </x:c>
+      <x:c r="H103" s="31" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I103" s="28" t="str"/>
+      <x:c r="J103" s="28" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="K103" s="28" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="L103" s="34" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="M103" s="28" t="str"/>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" s="37" t="str">
+        <x:v>TRY-00800</x:v>
+      </x:c>
+      <x:c r="B104" s="28" t="str">
+        <x:v>ABL borrowing base and covenant cure</x:v>
+      </x:c>
+      <x:c r="C104" s="28" t="str">
+        <x:v>Detailed AR collateral control</x:v>
+      </x:c>
+      <x:c r="D104" s="28" t="str">
+        <x:v>Other and affiliate</x:v>
+      </x:c>
+      <x:c r="E104" s="28" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="F104" s="28" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="G104" s="28" t="str">
+        <x:v>Related-party exclusion</x:v>
+      </x:c>
+      <x:c r="H104" s="31" t="n">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="I104" s="28" t="str"/>
+      <x:c r="J104" s="28" t="str">
+        <x:v>USD thousands</x:v>
+      </x:c>
+      <x:c r="K104" s="28" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="L104" s="34" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="M104" s="28" t="str"/>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" s="37" t="str">
+        <x:v>TRY-00801</x:v>
+      </x:c>
+      <x:c r="B105" s="28" t="str">
+        <x:v>ABL borrowing base and covenant cure</x:v>
+      </x:c>
+      <x:c r="C105" s="28" t="str">
+        <x:v>Detailed inventory collateral control</x:v>
+      </x:c>
+      <x:c r="D105" s="28" t="str">
+        <x:v>Raw material</x:v>
+      </x:c>
+      <x:c r="E105" s="28" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="F105" s="28" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="G105" s="28" t="str">
+        <x:v>Gross inventory</x:v>
+      </x:c>
+      <x:c r="H105" s="31" t="n">
+        <x:v>3000000</x:v>
+      </x:c>
+      <x:c r="I105" s="28" t="str"/>
+      <x:c r="J105" s="28" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="K105" s="28" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="L105" s="34" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="M105" s="28" t="str"/>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" s="37" t="str">
+        <x:v>TRY-00802</x:v>
+      </x:c>
+      <x:c r="B106" s="28" t="str">
+        <x:v>ABL borrowing base and covenant cure</x:v>
+      </x:c>
+      <x:c r="C106" s="28" t="str">
+        <x:v>Detailed inventory collateral control</x:v>
+      </x:c>
+      <x:c r="D106" s="28" t="str">
+        <x:v>Raw material</x:v>
+      </x:c>
+      <x:c r="E106" s="28" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="F106" s="28" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="G106" s="28" t="str">
+        <x:v>Eligibility factor</x:v>
+      </x:c>
+      <x:c r="H106" s="31" t="n">
+        <x:v>0.95</x:v>
+      </x:c>
+      <x:c r="I106" s="28" t="str"/>
+      <x:c r="J106" s="28" t="str">
         <x:v>decimal ratio</x:v>
       </x:c>
-      <x:c r="K93" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
-      </x:c>
-      <x:c r="L93" s="34" t="str">
-        <x:v>2026-06-30</x:v>
-      </x:c>
-      <x:c r="M93" s="28" t="str"/>
-    </x:row>
-    <x:row r="94">
-      <x:c r="A94" s="38" t="str">
-        <x:v>TRY-00790</x:v>
-      </x:c>
-      <x:c r="B94" s="29" t="str">
+      <x:c r="K106" s="28" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="L106" s="34" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="M106" s="28" t="str"/>
+    </x:row>
+    <x:row r="107">
+      <x:c r="A107" s="37" t="str">
+        <x:v>TRY-00803</x:v>
+      </x:c>
+      <x:c r="B107" s="28" t="str">
         <x:v>ABL borrowing base and covenant cure</x:v>
       </x:c>
-      <x:c r="C94" s="29" t="str">
+      <x:c r="C107" s="28" t="str">
+        <x:v>Detailed inventory collateral control</x:v>
+      </x:c>
+      <x:c r="D107" s="28" t="str">
+        <x:v>Work in process</x:v>
+      </x:c>
+      <x:c r="E107" s="28" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="F107" s="28" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="G107" s="28" t="str">
+        <x:v>Gross inventory</x:v>
+      </x:c>
+      <x:c r="H107" s="31" t="n">
+        <x:v>1400000</x:v>
+      </x:c>
+      <x:c r="I107" s="28" t="str"/>
+      <x:c r="J107" s="28" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="K107" s="28" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="L107" s="34" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="M107" s="28" t="str"/>
+    </x:row>
+    <x:row r="108">
+      <x:c r="A108" s="37" t="str">
+        <x:v>TRY-00804</x:v>
+      </x:c>
+      <x:c r="B108" s="28" t="str">
+        <x:v>ABL borrowing base and covenant cure</x:v>
+      </x:c>
+      <x:c r="C108" s="28" t="str">
+        <x:v>Detailed inventory collateral control</x:v>
+      </x:c>
+      <x:c r="D108" s="28" t="str">
+        <x:v>Work in process</x:v>
+      </x:c>
+      <x:c r="E108" s="28" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="F108" s="28" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="G108" s="28" t="str">
+        <x:v>Eligibility factor</x:v>
+      </x:c>
+      <x:c r="H108" s="31" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="I108" s="28" t="str"/>
+      <x:c r="J108" s="28" t="str">
+        <x:v>decimal ratio</x:v>
+      </x:c>
+      <x:c r="K108" s="28" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="L108" s="34" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="M108" s="28" t="str"/>
+    </x:row>
+    <x:row r="109">
+      <x:c r="A109" s="37" t="str">
+        <x:v>TRY-00805</x:v>
+      </x:c>
+      <x:c r="B109" s="28" t="str">
+        <x:v>ABL borrowing base and covenant cure</x:v>
+      </x:c>
+      <x:c r="C109" s="28" t="str">
+        <x:v>Detailed inventory collateral control</x:v>
+      </x:c>
+      <x:c r="D109" s="28" t="str">
+        <x:v>Finished goods</x:v>
+      </x:c>
+      <x:c r="E109" s="28" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="F109" s="28" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="G109" s="28" t="str">
+        <x:v>Gross inventory</x:v>
+      </x:c>
+      <x:c r="H109" s="31" t="n">
+        <x:v>1100000</x:v>
+      </x:c>
+      <x:c r="I109" s="28" t="str"/>
+      <x:c r="J109" s="28" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="K109" s="28" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="L109" s="34" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="M109" s="28" t="str"/>
+    </x:row>
+    <x:row r="110">
+      <x:c r="A110" s="37" t="str">
+        <x:v>TRY-00806</x:v>
+      </x:c>
+      <x:c r="B110" s="28" t="str">
+        <x:v>ABL borrowing base and covenant cure</x:v>
+      </x:c>
+      <x:c r="C110" s="28" t="str">
+        <x:v>Detailed inventory collateral control</x:v>
+      </x:c>
+      <x:c r="D110" s="28" t="str">
+        <x:v>Finished goods</x:v>
+      </x:c>
+      <x:c r="E110" s="28" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="F110" s="28" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="G110" s="28" t="str">
+        <x:v>Eligibility factor</x:v>
+      </x:c>
+      <x:c r="H110" s="31" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="I110" s="28" t="str"/>
+      <x:c r="J110" s="28" t="str">
+        <x:v>decimal ratio</x:v>
+      </x:c>
+      <x:c r="K110" s="28" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="L110" s="34" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="M110" s="28" t="str"/>
+    </x:row>
+    <x:row r="111">
+      <x:c r="A111" s="37" t="str">
+        <x:v>TRY-00807</x:v>
+      </x:c>
+      <x:c r="B111" s="28" t="str">
+        <x:v>ABL borrowing base and covenant cure</x:v>
+      </x:c>
+      <x:c r="C111" s="28" t="str">
         <x:v>Detailed ABL policy</x:v>
       </x:c>
-      <x:c r="D94" s="29" t="str">
+      <x:c r="D111" s="28" t="str">
         <x:v>Alder Ridge</x:v>
       </x:c>
-      <x:c r="E94" s="29" t="str">
-        <x:v>2026-06-30</x:v>
-      </x:c>
-      <x:c r="F94" s="29" t="str">
-        <x:v>Approved case</x:v>
-      </x:c>
-      <x:c r="G94" s="29" t="str">
+      <x:c r="E111" s="28" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="F111" s="28" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="G111" s="28" t="str">
+        <x:v>Single customer concentration cap</x:v>
+      </x:c>
+      <x:c r="H111" s="31" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="I111" s="28" t="str"/>
+      <x:c r="J111" s="28" t="str">
+        <x:v>decimal ratio</x:v>
+      </x:c>
+      <x:c r="K111" s="28" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="L111" s="34" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="M111" s="28" t="str"/>
+    </x:row>
+    <x:row r="112">
+      <x:c r="A112" s="38" t="str">
+        <x:v>TRY-00808</x:v>
+      </x:c>
+      <x:c r="B112" s="29" t="str">
+        <x:v>ABL borrowing base and covenant cure</x:v>
+      </x:c>
+      <x:c r="C112" s="29" t="str">
+        <x:v>Detailed ABL policy</x:v>
+      </x:c>
+      <x:c r="D112" s="29" t="str">
+        <x:v>Alder Ridge</x:v>
+      </x:c>
+      <x:c r="E112" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="F112" s="29" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="G112" s="29" t="str">
         <x:v>Facility basis</x:v>
       </x:c>
-      <x:c r="H94" s="32" t="str"/>
-      <x:c r="I94" s="29" t="str">
+      <x:c r="H112" s="32" t="str"/>
+      <x:c r="I112" s="29" t="str">
         <x:v>Controller-approved pro forma ABL alternative; not the executed current revolver</x:v>
       </x:c>
-      <x:c r="J94" s="29" t="str">
+      <x:c r="J112" s="29" t="str">
         <x:v>classification</x:v>
       </x:c>
-      <x:c r="K94" s="29" t="str">
-        <x:v>Finance operating schedule</x:v>
-      </x:c>
-      <x:c r="L94" s="35" t="str">
-        <x:v>2026-06-30</x:v>
-      </x:c>
-      <x:c r="M94" s="29" t="str"/>
+      <x:c r="K112" s="29" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="L112" s="35" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="M112" s="29" t="str"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -18741,11 +19407,11 @@
         <x:v>Credit Outlook</x:v>
       </x:c>
       <x:c r="B8" s="42" t="n">
-        <x:v>90</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C8" s="42" t="n">
-        <x:f>COUNTA('Credit Outlook'!$A$5:$A$94)</x:f>
-        <x:v>90</x:v>
+        <x:f>COUNTA('Credit Outlook'!$A$5:$A$112)</x:f>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D8" s="42" t="n">
         <x:f>C8-B8</x:f>
